--- a/apps/nuxt/i18n/i18n.xlsx
+++ b/apps/nuxt/i18n/i18n.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wysha_Object\wysha_Project\WebProjects\TypeWords\apps\nuxt\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB7D4BC-824B-407B-8236-16AECD6180B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE11512-4EEF-4B51-BFCC-DA6F5BCC09F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-16200" windowWidth="29010" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="-16200" windowWidth="29010" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7830" uniqueCount="7181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7920" uniqueCount="7194">
   <si>
     <t>key</t>
   </si>
@@ -21605,6 +21605,58 @@
   </si>
   <si>
     <t>在单次学习的整个过程中每个单词的错误次数会被用以给其评级,共有四个评级,Again,Hard,Good,Easy,FSRS算法会使用评级来计算这个单词下一次需要复习的时间,启用或禁用FSRS仅影响生成复习词的规则,不影响上述过程的执行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为下次复习时间引入一定的随机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过引入随机,可以避免大量单词需要在同一天复习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fsrs_advanced</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级设置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fsrs_advanced_weight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>权重</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fsrs_advanced_request_retention</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希望的最小回忆概率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fsrs_advanced_enable_fuzz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fsrs_advanced_enable_fuzz_desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大天数限制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fsrs_advanced_maximum_interval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大间隔天数限制</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -21612,7 +21664,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -21635,6 +21687,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -21656,11 +21714,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -22001,7 +22062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O522"/>
+  <dimension ref="A1:O528"/>
   <sheetFormatPr defaultColWidth="9.625" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
@@ -46542,6 +46603,288 @@
         <v>7179</v>
       </c>
     </row>
+    <row r="523" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A523" s="1" t="s">
+        <v>7183</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>7184</v>
+      </c>
+      <c r="C523" s="1" t="s">
+        <v>7184</v>
+      </c>
+      <c r="D523" s="1" t="s">
+        <v>7184</v>
+      </c>
+      <c r="E523" s="1" t="s">
+        <v>7184</v>
+      </c>
+      <c r="F523" s="1" t="s">
+        <v>7184</v>
+      </c>
+      <c r="G523" s="1" t="s">
+        <v>7184</v>
+      </c>
+      <c r="H523" s="1" t="s">
+        <v>7184</v>
+      </c>
+      <c r="I523" s="1" t="s">
+        <v>7184</v>
+      </c>
+      <c r="J523" s="1" t="s">
+        <v>7184</v>
+      </c>
+      <c r="K523" s="1" t="s">
+        <v>7184</v>
+      </c>
+      <c r="L523" s="1" t="s">
+        <v>7184</v>
+      </c>
+      <c r="M523" s="1" t="s">
+        <v>7184</v>
+      </c>
+      <c r="N523" s="1" t="s">
+        <v>7184</v>
+      </c>
+      <c r="O523" s="1" t="s">
+        <v>7184</v>
+      </c>
+    </row>
+    <row r="524" spans="1:15" ht="15" x14ac:dyDescent="0.15">
+      <c r="A524" s="3" t="s">
+        <v>7189</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>7181</v>
+      </c>
+      <c r="C524" s="1" t="s">
+        <v>7181</v>
+      </c>
+      <c r="D524" s="1" t="s">
+        <v>7181</v>
+      </c>
+      <c r="E524" s="1" t="s">
+        <v>7181</v>
+      </c>
+      <c r="F524" s="1" t="s">
+        <v>7181</v>
+      </c>
+      <c r="G524" s="1" t="s">
+        <v>7181</v>
+      </c>
+      <c r="H524" s="1" t="s">
+        <v>7181</v>
+      </c>
+      <c r="I524" s="1" t="s">
+        <v>7181</v>
+      </c>
+      <c r="J524" s="1" t="s">
+        <v>7181</v>
+      </c>
+      <c r="K524" s="1" t="s">
+        <v>7181</v>
+      </c>
+      <c r="L524" s="1" t="s">
+        <v>7181</v>
+      </c>
+      <c r="M524" s="1" t="s">
+        <v>7181</v>
+      </c>
+      <c r="N524" s="1" t="s">
+        <v>7181</v>
+      </c>
+      <c r="O524" s="1" t="s">
+        <v>7181</v>
+      </c>
+    </row>
+    <row r="525" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A525" s="1" t="s">
+        <v>7190</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>7182</v>
+      </c>
+      <c r="C525" s="1" t="s">
+        <v>7182</v>
+      </c>
+      <c r="D525" s="1" t="s">
+        <v>7182</v>
+      </c>
+      <c r="E525" s="1" t="s">
+        <v>7182</v>
+      </c>
+      <c r="F525" s="1" t="s">
+        <v>7182</v>
+      </c>
+      <c r="G525" s="1" t="s">
+        <v>7182</v>
+      </c>
+      <c r="H525" s="1" t="s">
+        <v>7182</v>
+      </c>
+      <c r="I525" s="1" t="s">
+        <v>7182</v>
+      </c>
+      <c r="J525" s="1" t="s">
+        <v>7182</v>
+      </c>
+      <c r="K525" s="1" t="s">
+        <v>7182</v>
+      </c>
+      <c r="L525" s="1" t="s">
+        <v>7182</v>
+      </c>
+      <c r="M525" s="1" t="s">
+        <v>7182</v>
+      </c>
+      <c r="N525" s="1" t="s">
+        <v>7182</v>
+      </c>
+      <c r="O525" s="1" t="s">
+        <v>7182</v>
+      </c>
+    </row>
+    <row r="526" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A526" s="1" t="s">
+        <v>7185</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>7186</v>
+      </c>
+      <c r="C526" s="1" t="s">
+        <v>7186</v>
+      </c>
+      <c r="D526" s="1" t="s">
+        <v>7186</v>
+      </c>
+      <c r="E526" s="1" t="s">
+        <v>7186</v>
+      </c>
+      <c r="F526" s="1" t="s">
+        <v>7186</v>
+      </c>
+      <c r="G526" s="1" t="s">
+        <v>7186</v>
+      </c>
+      <c r="H526" s="1" t="s">
+        <v>7186</v>
+      </c>
+      <c r="I526" s="1" t="s">
+        <v>7186</v>
+      </c>
+      <c r="J526" s="1" t="s">
+        <v>7186</v>
+      </c>
+      <c r="K526" s="1" t="s">
+        <v>7186</v>
+      </c>
+      <c r="L526" s="1" t="s">
+        <v>7186</v>
+      </c>
+      <c r="M526" s="1" t="s">
+        <v>7186</v>
+      </c>
+      <c r="N526" s="1" t="s">
+        <v>7186</v>
+      </c>
+      <c r="O526" s="1" t="s">
+        <v>7186</v>
+      </c>
+    </row>
+    <row r="527" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A527" s="1" t="s">
+        <v>7187</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>7188</v>
+      </c>
+      <c r="C527" s="1" t="s">
+        <v>7188</v>
+      </c>
+      <c r="D527" s="1" t="s">
+        <v>7188</v>
+      </c>
+      <c r="E527" s="1" t="s">
+        <v>7188</v>
+      </c>
+      <c r="F527" s="1" t="s">
+        <v>7188</v>
+      </c>
+      <c r="G527" s="1" t="s">
+        <v>7188</v>
+      </c>
+      <c r="H527" s="1" t="s">
+        <v>7188</v>
+      </c>
+      <c r="I527" s="1" t="s">
+        <v>7188</v>
+      </c>
+      <c r="J527" s="1" t="s">
+        <v>7188</v>
+      </c>
+      <c r="K527" s="1" t="s">
+        <v>7188</v>
+      </c>
+      <c r="L527" s="1" t="s">
+        <v>7188</v>
+      </c>
+      <c r="M527" s="1" t="s">
+        <v>7188</v>
+      </c>
+      <c r="N527" s="1" t="s">
+        <v>7188</v>
+      </c>
+      <c r="O527" s="1" t="s">
+        <v>7188</v>
+      </c>
+    </row>
+    <row r="528" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A528" s="1" t="s">
+        <v>7192</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>7193</v>
+      </c>
+      <c r="C528" s="1" t="s">
+        <v>7191</v>
+      </c>
+      <c r="D528" s="1" t="s">
+        <v>7191</v>
+      </c>
+      <c r="E528" s="1" t="s">
+        <v>7191</v>
+      </c>
+      <c r="F528" s="1" t="s">
+        <v>7191</v>
+      </c>
+      <c r="G528" s="1" t="s">
+        <v>7191</v>
+      </c>
+      <c r="H528" s="1" t="s">
+        <v>7191</v>
+      </c>
+      <c r="I528" s="1" t="s">
+        <v>7191</v>
+      </c>
+      <c r="J528" s="1" t="s">
+        <v>7191</v>
+      </c>
+      <c r="K528" s="1" t="s">
+        <v>7191</v>
+      </c>
+      <c r="L528" s="1" t="s">
+        <v>7191</v>
+      </c>
+      <c r="M528" s="1" t="s">
+        <v>7191</v>
+      </c>
+      <c r="N528" s="1" t="s">
+        <v>7191</v>
+      </c>
+      <c r="O528" s="1" t="s">
+        <v>7191</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/apps/nuxt/i18n/i18n.xlsx
+++ b/apps/nuxt/i18n/i18n.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wysha_Object\wysha_Project\WebProjects\TypeWords\apps\nuxt\i18n\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE11512-4EEF-4B51-BFCC-DA6F5BCC09F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-16200" windowWidth="29010" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="25600" windowHeight="12200"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7920" uniqueCount="7194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7920" uniqueCount="7195">
   <si>
     <t>key</t>
   </si>
@@ -21535,136 +21529,116 @@
     <t>enable_fsrs</t>
   </si>
   <si>
-    <t>启用FSRS</t>
+    <t>启用遗忘曲线算法</t>
   </si>
   <si>
     <t>enable_fsrs_desc</t>
   </si>
   <si>
+    <t>开启后，将使用遗忘曲线(FSRS)算法来决定需要复习的单词,而非固定单词数量; 刚启用时，没有复习词，学习一次之后才有复习词</t>
+  </si>
+  <si>
     <t>开启后，将使用FSRS算法来决定需要复习的单词,而非固定单词数量</t>
   </si>
   <si>
     <t>fsrs_settings</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FSRS设置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遗忘曲线设置</t>
+  </si>
+  <si>
+    <t>fsrs_limit_desc</t>
+  </si>
+  <si>
+    <t>在学习过程中对每个单词错误次数进行评级，共有四个评级，Again,Hard,Good,Easy，遗忘曲线算法会使用评级来计算这个单词下一次需要复习的时间。</t>
   </si>
   <si>
     <t>fsrs_easy_limit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Easy评级判定标准</t>
   </si>
   <si>
     <t>fsrs_good_limit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Good评级判定标准</t>
   </si>
   <si>
     <t>fsrs_hard_limit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Easy评级判定标准</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Good评级判定标准</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Hard评级判定标准</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fsrs_limit_desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>less_or_equals</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小于等于</t>
   </si>
   <si>
     <t>times</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>次</t>
   </si>
   <si>
     <t>wrong</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小于等于</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在单次学习的整个过程中每个单词的错误次数会被用以给其评级,共有四个评级,Again,Hard,Good,Easy,FSRS算法会使用评级来计算这个单词下一次需要复习的时间,启用或禁用FSRS仅影响生成复习词的规则,不影响上述过程的执行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fsrs_advanced</t>
+  </si>
+  <si>
+    <t>高级设置</t>
+  </si>
+  <si>
+    <t>fsrs_advanced_enable_fuzz</t>
   </si>
   <si>
     <t>为下次复习时间引入一定的随机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fsrs_advanced_enable_fuzz_desc</t>
   </si>
   <si>
     <t>通过引入随机,可以避免大量单词需要在同一天复习</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fsrs_advanced</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高级设置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>fsrs_advanced_weight</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>权重</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>fsrs_advanced_request_retention</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>希望的最小回忆概率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fsrs_advanced_enable_fuzz</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fsrs_advanced_enable_fuzz_desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fsrs_advanced_maximum_interval</t>
+  </si>
+  <si>
+    <t>最大间隔天数限制</t>
   </si>
   <si>
     <t>最大天数限制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fsrs_advanced_maximum_interval</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最大间隔天数限制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -21673,17 +21647,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -21691,18 +21657,355 @@
       <sz val="11"/>
       <color rgb="FFCE9178"/>
       <name val="Consolas"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -21710,31 +22013,318 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -22056,20 +22646,20 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O528"/>
-  <sheetFormatPr defaultColWidth="9.625" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
     <col min="2" max="2" width="21.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -22116,7 +22706,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -22163,7 +22753,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -22210,7 +22800,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -22257,7 +22847,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -22304,7 +22894,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -22351,7 +22941,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>77</v>
       </c>
@@ -22398,7 +22988,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -22445,7 +23035,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>107</v>
       </c>
@@ -22492,7 +23082,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>122</v>
       </c>
@@ -22539,7 +23129,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -22586,7 +23176,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>150</v>
       </c>
@@ -22633,7 +23223,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>165</v>
       </c>
@@ -22680,7 +23270,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
         <v>180</v>
       </c>
@@ -22727,7 +23317,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
         <v>195</v>
       </c>
@@ -22774,7 +23364,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
         <v>210</v>
       </c>
@@ -22821,7 +23411,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
         <v>225</v>
       </c>
@@ -22868,7 +23458,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
         <v>240</v>
       </c>
@@ -22915,7 +23505,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
         <v>255</v>
       </c>
@@ -22962,7 +23552,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
         <v>270</v>
       </c>
@@ -23009,7 +23599,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
         <v>285</v>
       </c>
@@ -23056,7 +23646,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
         <v>300</v>
       </c>
@@ -23103,7 +23693,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
         <v>314</v>
       </c>
@@ -23150,7 +23740,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
         <v>328</v>
       </c>
@@ -23197,7 +23787,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
         <v>342</v>
       </c>
@@ -23244,7 +23834,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
         <v>357</v>
       </c>
@@ -23291,7 +23881,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
         <v>372</v>
       </c>
@@ -23338,7 +23928,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
         <v>387</v>
       </c>
@@ -23385,7 +23975,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
         <v>402</v>
       </c>
@@ -23432,7 +24022,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
         <v>417</v>
       </c>
@@ -23479,7 +24069,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:15">
       <c r="A31" t="s">
         <v>432</v>
       </c>
@@ -23526,7 +24116,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
         <v>447</v>
       </c>
@@ -23573,7 +24163,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:15">
       <c r="A33" t="s">
         <v>462</v>
       </c>
@@ -23620,7 +24210,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:15">
       <c r="A34" t="s">
         <v>477</v>
       </c>
@@ -23667,7 +24257,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:15">
       <c r="A35" t="s">
         <v>492</v>
       </c>
@@ -23714,7 +24304,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:15">
       <c r="A36" t="s">
         <v>507</v>
       </c>
@@ -23761,7 +24351,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:15">
       <c r="A37" t="s">
         <v>510</v>
       </c>
@@ -23808,7 +24398,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:15">
       <c r="A38" t="s">
         <v>513</v>
       </c>
@@ -23855,7 +24445,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:15">
       <c r="A39" t="s">
         <v>528</v>
       </c>
@@ -23902,7 +24492,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:15">
       <c r="A40" t="s">
         <v>541</v>
       </c>
@@ -23949,7 +24539,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:15">
       <c r="A41" t="s">
         <v>556</v>
       </c>
@@ -23996,7 +24586,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:15">
       <c r="A42" t="s">
         <v>569</v>
       </c>
@@ -24043,7 +24633,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:15">
       <c r="A43" t="s">
         <v>582</v>
       </c>
@@ -24090,7 +24680,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:15">
       <c r="A44" t="s">
         <v>595</v>
       </c>
@@ -24137,7 +24727,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:15">
       <c r="A45" t="s">
         <v>610</v>
       </c>
@@ -24184,7 +24774,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:15">
       <c r="A46" t="s">
         <v>624</v>
       </c>
@@ -24231,7 +24821,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:15">
       <c r="A47" t="s">
         <v>638</v>
       </c>
@@ -24278,7 +24868,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:15">
       <c r="A48" t="s">
         <v>653</v>
       </c>
@@ -24325,7 +24915,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:15">
       <c r="A49" t="s">
         <v>667</v>
       </c>
@@ -24372,7 +24962,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:15">
       <c r="A50" t="s">
         <v>681</v>
       </c>
@@ -24419,7 +25009,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:15">
       <c r="A51" t="s">
         <v>694</v>
       </c>
@@ -24466,7 +25056,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:15">
       <c r="A52" t="s">
         <v>706</v>
       </c>
@@ -24513,7 +25103,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:15">
       <c r="A53" t="s">
         <v>719</v>
       </c>
@@ -24560,7 +25150,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:15">
       <c r="A54" t="s">
         <v>732</v>
       </c>
@@ -24607,7 +25197,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:15">
       <c r="A55" t="s">
         <v>747</v>
       </c>
@@ -24654,7 +25244,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:15">
       <c r="A56" t="s">
         <v>760</v>
       </c>
@@ -24701,7 +25291,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:15">
       <c r="A57" t="s">
         <v>775</v>
       </c>
@@ -24748,7 +25338,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:15">
       <c r="A58" t="s">
         <v>790</v>
       </c>
@@ -24795,7 +25385,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:15">
       <c r="A59" t="s">
         <v>805</v>
       </c>
@@ -24842,7 +25432,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:15">
       <c r="A60" t="s">
         <v>820</v>
       </c>
@@ -24889,7 +25479,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:15">
       <c r="A61" t="s">
         <v>835</v>
       </c>
@@ -24936,7 +25526,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:15">
       <c r="A62" t="s">
         <v>850</v>
       </c>
@@ -24983,7 +25573,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:15">
       <c r="A63" t="s">
         <v>865</v>
       </c>
@@ -25030,7 +25620,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:15">
       <c r="A64" t="s">
         <v>880</v>
       </c>
@@ -25077,7 +25667,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:15">
       <c r="A65" t="s">
         <v>895</v>
       </c>
@@ -25124,7 +25714,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:15">
       <c r="A66" t="s">
         <v>910</v>
       </c>
@@ -25171,7 +25761,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:15">
       <c r="A67" t="s">
         <v>925</v>
       </c>
@@ -25218,7 +25808,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:15">
       <c r="A68" t="s">
         <v>940</v>
       </c>
@@ -25265,7 +25855,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:15">
       <c r="A69" t="s">
         <v>955</v>
       </c>
@@ -25312,7 +25902,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:15">
       <c r="A70" t="s">
         <v>970</v>
       </c>
@@ -25359,7 +25949,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:15">
       <c r="A71" t="s">
         <v>985</v>
       </c>
@@ -25406,7 +25996,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:15">
       <c r="A72" t="s">
         <v>1000</v>
       </c>
@@ -25453,7 +26043,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:15">
       <c r="A73" t="s">
         <v>1015</v>
       </c>
@@ -25500,7 +26090,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:15">
       <c r="A74" t="s">
         <v>1030</v>
       </c>
@@ -25547,7 +26137,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:15">
       <c r="A75" t="s">
         <v>1045</v>
       </c>
@@ -25594,7 +26184,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:15">
       <c r="A76" t="s">
         <v>1060</v>
       </c>
@@ -25641,7 +26231,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:15">
       <c r="A77" t="s">
         <v>1075</v>
       </c>
@@ -25688,7 +26278,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:15">
       <c r="A78" t="s">
         <v>1090</v>
       </c>
@@ -25735,7 +26325,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:15">
       <c r="A79" t="s">
         <v>1105</v>
       </c>
@@ -25782,7 +26372,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:15">
       <c r="A80" t="s">
         <v>1120</v>
       </c>
@@ -25829,7 +26419,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:15">
       <c r="A81" t="s">
         <v>1135</v>
       </c>
@@ -25876,7 +26466,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:15">
       <c r="A82" t="s">
         <v>1149</v>
       </c>
@@ -25923,7 +26513,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:15">
       <c r="A83" t="s">
         <v>1162</v>
       </c>
@@ -25970,7 +26560,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:15">
       <c r="A84" t="s">
         <v>1173</v>
       </c>
@@ -26017,7 +26607,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:15">
       <c r="A85" t="s">
         <v>1188</v>
       </c>
@@ -26064,7 +26654,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:15">
       <c r="A86" t="s">
         <v>1202</v>
       </c>
@@ -26111,7 +26701,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:15">
       <c r="A87" t="s">
         <v>1217</v>
       </c>
@@ -26158,7 +26748,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:15">
       <c r="A88" t="s">
         <v>1232</v>
       </c>
@@ -26205,7 +26795,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:15">
       <c r="A89" t="s">
         <v>1247</v>
       </c>
@@ -26252,7 +26842,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:15">
       <c r="A90" t="s">
         <v>1262</v>
       </c>
@@ -26299,7 +26889,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:15">
       <c r="A91" t="s">
         <v>1277</v>
       </c>
@@ -26346,7 +26936,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:15">
       <c r="A92" t="s">
         <v>1292</v>
       </c>
@@ -26393,7 +26983,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:15">
       <c r="A93" t="s">
         <v>1307</v>
       </c>
@@ -26440,7 +27030,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:15">
       <c r="A94" t="s">
         <v>1321</v>
       </c>
@@ -26487,7 +27077,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:15">
       <c r="A95" t="s">
         <v>1336</v>
       </c>
@@ -26534,7 +27124,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:15">
       <c r="A96" t="s">
         <v>1351</v>
       </c>
@@ -26581,7 +27171,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:15">
       <c r="A97" t="s">
         <v>1366</v>
       </c>
@@ -26628,7 +27218,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:15">
       <c r="A98" t="s">
         <v>1381</v>
       </c>
@@ -26675,7 +27265,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:15">
       <c r="A99" t="s">
         <v>1396</v>
       </c>
@@ -26722,7 +27312,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:15">
       <c r="A100" t="s">
         <v>1411</v>
       </c>
@@ -26769,7 +27359,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:15">
       <c r="A101" t="s">
         <v>1426</v>
       </c>
@@ -26816,7 +27406,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:15">
       <c r="A102" t="s">
         <v>1441</v>
       </c>
@@ -26863,7 +27453,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:15">
       <c r="A103" t="s">
         <v>1456</v>
       </c>
@@ -26910,7 +27500,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:15">
       <c r="A104" t="s">
         <v>1470</v>
       </c>
@@ -26957,7 +27547,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:15">
       <c r="A105" t="s">
         <v>1485</v>
       </c>
@@ -27004,7 +27594,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:15">
       <c r="A106" t="s">
         <v>1500</v>
       </c>
@@ -27051,7 +27641,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:15">
       <c r="A107" t="s">
         <v>1515</v>
       </c>
@@ -27098,7 +27688,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:15">
       <c r="A108" t="s">
         <v>1530</v>
       </c>
@@ -27145,7 +27735,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:15">
       <c r="A109" t="s">
         <v>1545</v>
       </c>
@@ -27192,7 +27782,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:15">
       <c r="A110" t="s">
         <v>1560</v>
       </c>
@@ -27239,7 +27829,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:15">
       <c r="A111" t="s">
         <v>1574</v>
       </c>
@@ -27286,7 +27876,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:15">
       <c r="A112" t="s">
         <v>1589</v>
       </c>
@@ -27333,7 +27923,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:15">
       <c r="A113" t="s">
         <v>1604</v>
       </c>
@@ -27380,7 +27970,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:15">
       <c r="A114" t="s">
         <v>1619</v>
       </c>
@@ -27427,7 +28017,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:15">
       <c r="A115" t="s">
         <v>1634</v>
       </c>
@@ -27474,7 +28064,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:15">
       <c r="A116" t="s">
         <v>1649</v>
       </c>
@@ -27521,7 +28111,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:15">
       <c r="A117" t="s">
         <v>1660</v>
       </c>
@@ -27568,7 +28158,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:15">
       <c r="A118" t="s">
         <v>1673</v>
       </c>
@@ -27615,7 +28205,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:15">
       <c r="A119" t="s">
         <v>1688</v>
       </c>
@@ -27662,7 +28252,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:15">
       <c r="A120" t="s">
         <v>1702</v>
       </c>
@@ -27709,7 +28299,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:15">
       <c r="A121" t="s">
         <v>1715</v>
       </c>
@@ -27756,7 +28346,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:15">
       <c r="A122" t="s">
         <v>1730</v>
       </c>
@@ -27803,7 +28393,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:15">
       <c r="A123" t="s">
         <v>1745</v>
       </c>
@@ -27850,7 +28440,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:15">
       <c r="A124" t="s">
         <v>1759</v>
       </c>
@@ -27897,7 +28487,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:15">
       <c r="A125" t="s">
         <v>1774</v>
       </c>
@@ -27944,7 +28534,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:15">
       <c r="A126" t="s">
         <v>1789</v>
       </c>
@@ -27991,7 +28581,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:15">
       <c r="A127" t="s">
         <v>1804</v>
       </c>
@@ -28038,7 +28628,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:15">
       <c r="A128" t="s">
         <v>1819</v>
       </c>
@@ -28085,7 +28675,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:15">
       <c r="A129" t="s">
         <v>1834</v>
       </c>
@@ -28132,7 +28722,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:15">
       <c r="A130" t="s">
         <v>1849</v>
       </c>
@@ -28179,7 +28769,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:15">
       <c r="A131" t="s">
         <v>1864</v>
       </c>
@@ -28226,7 +28816,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:15">
       <c r="A132" t="s">
         <v>1877</v>
       </c>
@@ -28273,7 +28863,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:15">
       <c r="A133" t="s">
         <v>1889</v>
       </c>
@@ -28320,7 +28910,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:15">
       <c r="A134" t="s">
         <v>1904</v>
       </c>
@@ -28367,7 +28957,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:15">
       <c r="A135" t="s">
         <v>1909</v>
       </c>
@@ -28414,7 +29004,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:15">
       <c r="A136" t="s">
         <v>1924</v>
       </c>
@@ -28461,7 +29051,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:15">
       <c r="A137" t="s">
         <v>1939</v>
       </c>
@@ -28508,7 +29098,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:15">
       <c r="A138" t="s">
         <v>1954</v>
       </c>
@@ -28555,7 +29145,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:15">
       <c r="A139" t="s">
         <v>1969</v>
       </c>
@@ -28602,7 +29192,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:15">
       <c r="A140" t="s">
         <v>1984</v>
       </c>
@@ -28649,7 +29239,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:15">
       <c r="A141" t="s">
         <v>1999</v>
       </c>
@@ -28696,7 +29286,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:15">
       <c r="A142" t="s">
         <v>2013</v>
       </c>
@@ -28743,7 +29333,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:15">
       <c r="A143" t="s">
         <v>2028</v>
       </c>
@@ -28790,7 +29380,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:15">
       <c r="A144" t="s">
         <v>2043</v>
       </c>
@@ -28837,7 +29427,7 @@
         <v>2057</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:15">
       <c r="A145" t="s">
         <v>2058</v>
       </c>
@@ -28884,7 +29474,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:15">
       <c r="A146" t="s">
         <v>2073</v>
       </c>
@@ -28931,7 +29521,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:15">
       <c r="A147" t="s">
         <v>2088</v>
       </c>
@@ -28978,7 +29568,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:15">
       <c r="A148" t="s">
         <v>2102</v>
       </c>
@@ -29025,7 +29615,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:15">
       <c r="A149" t="s">
         <v>2117</v>
       </c>
@@ -29072,7 +29662,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:15">
       <c r="A150" t="s">
         <v>2132</v>
       </c>
@@ -29119,7 +29709,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:15">
       <c r="A151" t="s">
         <v>2147</v>
       </c>
@@ -29166,7 +29756,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:15">
       <c r="A152" t="s">
         <v>2162</v>
       </c>
@@ -29213,7 +29803,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:15">
       <c r="A153" t="s">
         <v>2177</v>
       </c>
@@ -29260,7 +29850,7 @@
         <v>2190</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:15">
       <c r="A154" t="s">
         <v>2191</v>
       </c>
@@ -29307,7 +29897,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:15">
       <c r="A155" t="s">
         <v>2197</v>
       </c>
@@ -29354,7 +29944,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:15">
       <c r="A156" t="s">
         <v>2210</v>
       </c>
@@ -29401,7 +29991,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:15">
       <c r="A157" t="s">
         <v>2225</v>
       </c>
@@ -29448,7 +30038,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:15">
       <c r="A158" t="s">
         <v>2239</v>
       </c>
@@ -29495,7 +30085,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:15">
       <c r="A159" t="s">
         <v>2250</v>
       </c>
@@ -29542,7 +30132,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:15">
       <c r="A160" t="s">
         <v>2264</v>
       </c>
@@ -29589,7 +30179,7 @@
         <v>2278</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:15">
       <c r="A161" t="s">
         <v>2279</v>
       </c>
@@ -29636,7 +30226,7 @@
         <v>2293</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:15">
       <c r="A162" t="s">
         <v>2294</v>
       </c>
@@ -29683,7 +30273,7 @@
         <v>2308</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:15">
       <c r="A163" t="s">
         <v>2309</v>
       </c>
@@ -29730,7 +30320,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:15">
       <c r="A164" t="s">
         <v>2324</v>
       </c>
@@ -29777,7 +30367,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:15">
       <c r="A165" t="s">
         <v>2339</v>
       </c>
@@ -29824,7 +30414,7 @@
         <v>2353</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:15">
       <c r="A166" t="s">
         <v>2354</v>
       </c>
@@ -29871,7 +30461,7 @@
         <v>2367</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:15">
       <c r="A167" t="s">
         <v>2368</v>
       </c>
@@ -29918,7 +30508,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:15">
       <c r="A168" t="s">
         <v>2382</v>
       </c>
@@ -29965,7 +30555,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:15">
       <c r="A169" t="s">
         <v>2394</v>
       </c>
@@ -30012,7 +30602,7 @@
         <v>2408</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:15">
       <c r="A170" t="s">
         <v>2409</v>
       </c>
@@ -30059,7 +30649,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:15">
       <c r="A171" t="s">
         <v>2424</v>
       </c>
@@ -30106,7 +30696,7 @@
         <v>2438</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:15">
       <c r="A172" t="s">
         <v>2439</v>
       </c>
@@ -30153,7 +30743,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:15">
       <c r="A173" t="s">
         <v>2454</v>
       </c>
@@ -30200,7 +30790,7 @@
         <v>2468</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:15">
       <c r="A174" t="s">
         <v>2469</v>
       </c>
@@ -30247,7 +30837,7 @@
         <v>2472</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:15">
       <c r="A175" t="s">
         <v>2481</v>
       </c>
@@ -30294,7 +30884,7 @@
         <v>2493</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:15">
       <c r="A176" t="s">
         <v>2494</v>
       </c>
@@ -30341,7 +30931,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:15">
       <c r="A177" t="s">
         <v>2509</v>
       </c>
@@ -30388,7 +30978,7 @@
         <v>2523</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:15">
       <c r="A178" t="s">
         <v>2524</v>
       </c>
@@ -30435,7 +31025,7 @@
         <v>2538</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:15">
       <c r="A179" t="s">
         <v>2539</v>
       </c>
@@ -30482,7 +31072,7 @@
         <v>2553</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:15">
       <c r="A180" t="s">
         <v>2554</v>
       </c>
@@ -30529,7 +31119,7 @@
         <v>2568</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:15">
       <c r="A181" t="s">
         <v>2569</v>
       </c>
@@ -30576,7 +31166,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:15">
       <c r="A182" t="s">
         <v>2583</v>
       </c>
@@ -30623,7 +31213,7 @@
         <v>2597</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:15">
       <c r="A183" t="s">
         <v>2598</v>
       </c>
@@ -30670,7 +31260,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:15">
       <c r="A184" t="s">
         <v>2612</v>
       </c>
@@ -30717,7 +31307,7 @@
         <v>2613</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:15">
       <c r="A185" t="s">
         <v>2624</v>
       </c>
@@ -30764,7 +31354,7 @@
         <v>2638</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:15">
       <c r="A186" t="s">
         <v>2639</v>
       </c>
@@ -30811,7 +31401,7 @@
         <v>2653</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:15">
       <c r="A187" t="s">
         <v>2654</v>
       </c>
@@ -30858,7 +31448,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:15">
       <c r="A188" t="s">
         <v>2669</v>
       </c>
@@ -30905,7 +31495,7 @@
         <v>2683</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:15">
       <c r="A189" t="s">
         <v>2684</v>
       </c>
@@ -30952,7 +31542,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:15">
       <c r="A190" t="s">
         <v>2699</v>
       </c>
@@ -30999,7 +31589,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:15">
       <c r="A191" t="s">
         <v>2714</v>
       </c>
@@ -31046,7 +31636,7 @@
         <v>2728</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:15">
       <c r="A192" t="s">
         <v>2729</v>
       </c>
@@ -31093,7 +31683,7 @@
         <v>2743</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:15">
       <c r="A193" t="s">
         <v>2744</v>
       </c>
@@ -31140,7 +31730,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:15">
       <c r="A194" t="s">
         <v>2759</v>
       </c>
@@ -31187,7 +31777,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:15">
       <c r="A195" t="s">
         <v>2773</v>
       </c>
@@ -31234,7 +31824,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:15">
       <c r="A196" t="s">
         <v>2786</v>
       </c>
@@ -31281,7 +31871,7 @@
         <v>2787</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:15">
       <c r="A197" t="s">
         <v>2798</v>
       </c>
@@ -31328,7 +31918,7 @@
         <v>2799</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:15">
       <c r="A198" t="s">
         <v>2812</v>
       </c>
@@ -31375,7 +31965,7 @@
         <v>2825</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:15">
       <c r="A199" t="s">
         <v>2826</v>
       </c>
@@ -31422,7 +32012,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:15">
       <c r="A200" t="s">
         <v>2840</v>
       </c>
@@ -31469,7 +32059,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:15">
       <c r="A201" t="s">
         <v>2855</v>
       </c>
@@ -31516,7 +32106,7 @@
         <v>2856</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:15">
       <c r="A202" t="s">
         <v>2859</v>
       </c>
@@ -31563,7 +32153,7 @@
         <v>2860</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:15">
       <c r="A203" t="s">
         <v>2873</v>
       </c>
@@ -31610,7 +32200,7 @@
         <v>2887</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:15">
       <c r="A204" t="s">
         <v>2888</v>
       </c>
@@ -31657,7 +32247,7 @@
         <v>2889</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:15">
       <c r="A205" t="s">
         <v>2902</v>
       </c>
@@ -31704,7 +32294,7 @@
         <v>2916</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:15">
       <c r="A206" t="s">
         <v>2917</v>
       </c>
@@ -31751,7 +32341,7 @@
         <v>2931</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:15">
       <c r="A207" t="s">
         <v>2932</v>
       </c>
@@ -31798,7 +32388,7 @@
         <v>2946</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:15">
       <c r="A208" t="s">
         <v>2947</v>
       </c>
@@ -31845,7 +32435,7 @@
         <v>2961</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:15">
       <c r="A209" t="s">
         <v>2962</v>
       </c>
@@ -31892,7 +32482,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:15">
       <c r="A210" t="s">
         <v>2977</v>
       </c>
@@ -31939,7 +32529,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:15">
       <c r="A211" t="s">
         <v>2988</v>
       </c>
@@ -31986,7 +32576,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:15">
       <c r="A212" t="s">
         <v>3002</v>
       </c>
@@ -32033,7 +32623,7 @@
         <v>3003</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:15">
       <c r="A213" t="s">
         <v>3016</v>
       </c>
@@ -32080,7 +32670,7 @@
         <v>3030</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:15">
       <c r="A214" t="s">
         <v>3031</v>
       </c>
@@ -32127,7 +32717,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:15">
       <c r="A215" t="s">
         <v>3044</v>
       </c>
@@ -32174,7 +32764,7 @@
         <v>3047</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:15">
       <c r="A216" t="s">
         <v>3048</v>
       </c>
@@ -32221,7 +32811,7 @@
         <v>3062</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:15">
       <c r="A217" t="s">
         <v>3063</v>
       </c>
@@ -32268,7 +32858,7 @@
         <v>3064</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:15">
       <c r="A218" t="s">
         <v>3067</v>
       </c>
@@ -32315,7 +32905,7 @@
         <v>3081</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:15">
       <c r="A219" t="s">
         <v>3082</v>
       </c>
@@ -32362,7 +32952,7 @@
         <v>3083</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:15">
       <c r="A220" t="s">
         <v>3092</v>
       </c>
@@ -32409,7 +32999,7 @@
         <v>3106</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:15">
       <c r="A221" t="s">
         <v>3107</v>
       </c>
@@ -32456,7 +33046,7 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:15">
       <c r="A222" t="s">
         <v>3121</v>
       </c>
@@ -32503,7 +33093,7 @@
         <v>3135</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:15">
       <c r="A223" t="s">
         <v>3136</v>
       </c>
@@ -32550,7 +33140,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:15">
       <c r="A224" t="s">
         <v>3151</v>
       </c>
@@ -32597,7 +33187,7 @@
         <v>3152</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:15">
       <c r="A225" t="s">
         <v>3164</v>
       </c>
@@ -32644,7 +33234,7 @@
         <v>3178</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:15">
       <c r="A226" t="s">
         <v>3179</v>
       </c>
@@ -32691,7 +33281,7 @@
         <v>3180</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:15">
       <c r="A227" t="s">
         <v>3192</v>
       </c>
@@ -32738,7 +33328,7 @@
         <v>3206</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:15">
       <c r="A228" t="s">
         <v>3207</v>
       </c>
@@ -32785,7 +33375,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:15">
       <c r="A229" t="s">
         <v>3222</v>
       </c>
@@ -32832,7 +33422,7 @@
         <v>3236</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:15">
       <c r="A230" t="s">
         <v>3237</v>
       </c>
@@ -32879,7 +33469,7 @@
         <v>3238</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:15">
       <c r="A231" t="s">
         <v>3251</v>
       </c>
@@ -32926,7 +33516,7 @@
         <v>3265</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:15">
       <c r="A232" t="s">
         <v>3266</v>
       </c>
@@ -32973,7 +33563,7 @@
         <v>3280</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:15">
       <c r="A233" t="s">
         <v>3281</v>
       </c>
@@ -33020,7 +33610,7 @@
         <v>3295</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:15">
       <c r="A234" t="s">
         <v>3296</v>
       </c>
@@ -33067,7 +33657,7 @@
         <v>3310</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:15">
       <c r="A235" t="s">
         <v>3311</v>
       </c>
@@ -33114,7 +33704,7 @@
         <v>3325</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:15">
       <c r="A236" t="s">
         <v>3326</v>
       </c>
@@ -33161,7 +33751,7 @@
         <v>3340</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:15">
       <c r="A237" t="s">
         <v>3341</v>
       </c>
@@ -33208,7 +33798,7 @@
         <v>3355</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:15">
       <c r="A238" t="s">
         <v>3356</v>
       </c>
@@ -33255,7 +33845,7 @@
         <v>3370</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:15">
       <c r="A239" t="s">
         <v>3371</v>
       </c>
@@ -33302,7 +33892,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:15">
       <c r="A240" t="s">
         <v>3385</v>
       </c>
@@ -33349,7 +33939,7 @@
         <v>3399</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:15">
       <c r="A241" t="s">
         <v>3400</v>
       </c>
@@ -33396,7 +33986,7 @@
         <v>3414</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:15">
       <c r="A242" t="s">
         <v>3415</v>
       </c>
@@ -33443,7 +34033,7 @@
         <v>3429</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:15">
       <c r="A243" t="s">
         <v>3430</v>
       </c>
@@ -33490,7 +34080,7 @@
         <v>3431</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:15">
       <c r="A244" t="s">
         <v>3443</v>
       </c>
@@ -33537,7 +34127,7 @@
         <v>3444</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:15">
       <c r="A245" t="s">
         <v>3457</v>
       </c>
@@ -33584,7 +34174,7 @@
         <v>3471</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:15">
       <c r="A246" t="s">
         <v>3472</v>
       </c>
@@ -33631,7 +34221,7 @@
         <v>3486</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:15">
       <c r="A247" t="s">
         <v>3487</v>
       </c>
@@ -33678,7 +34268,7 @@
         <v>3488</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:15">
       <c r="A248" t="s">
         <v>3497</v>
       </c>
@@ -33725,7 +34315,7 @@
         <v>3511</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:15">
       <c r="A249" t="s">
         <v>3512</v>
       </c>
@@ -33772,7 +34362,7 @@
         <v>3526</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:15">
       <c r="A250" t="s">
         <v>3527</v>
       </c>
@@ -33819,7 +34409,7 @@
         <v>3541</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:15">
       <c r="A251" t="s">
         <v>3542</v>
       </c>
@@ -33866,7 +34456,7 @@
         <v>3556</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:15">
       <c r="A252" t="s">
         <v>3557</v>
       </c>
@@ -33913,7 +34503,7 @@
         <v>3571</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:15">
       <c r="A253" t="s">
         <v>3572</v>
       </c>
@@ -33960,7 +34550,7 @@
         <v>3586</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:15">
       <c r="A254" t="s">
         <v>3587</v>
       </c>
@@ -34007,7 +34597,7 @@
         <v>3601</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:15">
       <c r="A255" t="s">
         <v>3602</v>
       </c>
@@ -34054,7 +34644,7 @@
         <v>3616</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:15">
       <c r="A256" t="s">
         <v>3617</v>
       </c>
@@ -34101,7 +34691,7 @@
         <v>3618</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:15">
       <c r="A257" t="s">
         <v>3631</v>
       </c>
@@ -34148,7 +34738,7 @@
         <v>3645</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:15">
       <c r="A258" t="s">
         <v>3646</v>
       </c>
@@ -34195,7 +34785,7 @@
         <v>3660</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:15">
       <c r="A259" t="s">
         <v>3661</v>
       </c>
@@ -34242,7 +34832,7 @@
         <v>3675</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:15">
       <c r="A260" t="s">
         <v>3676</v>
       </c>
@@ -34289,7 +34879,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:15">
       <c r="A261" t="s">
         <v>3691</v>
       </c>
@@ -34336,7 +34926,7 @@
         <v>3705</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:15">
       <c r="A262" t="s">
         <v>3706</v>
       </c>
@@ -34383,7 +34973,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:15">
       <c r="A263" t="s">
         <v>3721</v>
       </c>
@@ -34430,7 +35020,7 @@
         <v>3722</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:15">
       <c r="A264" t="s">
         <v>3730</v>
       </c>
@@ -34477,7 +35067,7 @@
         <v>3744</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:15">
       <c r="A265" t="s">
         <v>3745</v>
       </c>
@@ -34524,7 +35114,7 @@
         <v>3746</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:15">
       <c r="A266" t="s">
         <v>3759</v>
       </c>
@@ -34571,7 +35161,7 @@
         <v>3760</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:15">
       <c r="A267" t="s">
         <v>3773</v>
       </c>
@@ -34618,7 +35208,7 @@
         <v>3787</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:15">
       <c r="A268" t="s">
         <v>3788</v>
       </c>
@@ -34665,7 +35255,7 @@
         <v>3802</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:15">
       <c r="A269" t="s">
         <v>3803</v>
       </c>
@@ -34712,7 +35302,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:15">
       <c r="A270" t="s">
         <v>3804</v>
       </c>
@@ -34759,7 +35349,7 @@
         <v>3818</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:15">
       <c r="A271" t="s">
         <v>3819</v>
       </c>
@@ -34806,7 +35396,7 @@
         <v>3833</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:15">
       <c r="A272" t="s">
         <v>3834</v>
       </c>
@@ -34853,7 +35443,7 @@
         <v>3835</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:15">
       <c r="A273" t="s">
         <v>3844</v>
       </c>
@@ -34900,7 +35490,7 @@
         <v>3845</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:15">
       <c r="A274" t="s">
         <v>3857</v>
       </c>
@@ -34947,7 +35537,7 @@
         <v>3858</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:15">
       <c r="A275" t="s">
         <v>3871</v>
       </c>
@@ -34994,7 +35584,7 @@
         <v>3872</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:15">
       <c r="A276" t="s">
         <v>3885</v>
       </c>
@@ -35041,7 +35631,7 @@
         <v>3898</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:15">
       <c r="A277" t="s">
         <v>3899</v>
       </c>
@@ -35088,7 +35678,7 @@
         <v>3902</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:15">
       <c r="A278" t="s">
         <v>3903</v>
       </c>
@@ -35135,7 +35725,7 @@
         <v>3915</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:15">
       <c r="A279" t="s">
         <v>3916</v>
       </c>
@@ -35182,7 +35772,7 @@
         <v>3930</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:15">
       <c r="A280" t="s">
         <v>3931</v>
       </c>
@@ -35229,7 +35819,7 @@
         <v>3945</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:15">
       <c r="A281" t="s">
         <v>3946</v>
       </c>
@@ -35276,7 +35866,7 @@
         <v>3960</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:15">
       <c r="A282" t="s">
         <v>3961</v>
       </c>
@@ -35323,7 +35913,7 @@
         <v>3975</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:15">
       <c r="A283" t="s">
         <v>3976</v>
       </c>
@@ -35370,7 +35960,7 @@
         <v>3990</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:15">
       <c r="A284" t="s">
         <v>3991</v>
       </c>
@@ -35417,7 +36007,7 @@
         <v>4005</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:15">
       <c r="A285" t="s">
         <v>4006</v>
       </c>
@@ -35464,7 +36054,7 @@
         <v>4020</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:15">
       <c r="A286" t="s">
         <v>4021</v>
       </c>
@@ -35511,7 +36101,7 @@
         <v>4035</v>
       </c>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:15">
       <c r="A287" t="s">
         <v>4036</v>
       </c>
@@ -35558,7 +36148,7 @@
         <v>4050</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:15">
       <c r="A288" t="s">
         <v>4051</v>
       </c>
@@ -35605,7 +36195,7 @@
         <v>4052</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:15">
       <c r="A289" t="s">
         <v>4065</v>
       </c>
@@ -35652,7 +36242,7 @@
         <v>4079</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:15">
       <c r="A290" t="s">
         <v>4080</v>
       </c>
@@ -35699,7 +36289,7 @@
         <v>4081</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:15">
       <c r="A291" t="s">
         <v>4094</v>
       </c>
@@ -35746,7 +36336,7 @@
         <v>4107</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:15">
       <c r="A292" t="s">
         <v>4108</v>
       </c>
@@ -35793,7 +36383,7 @@
         <v>4115</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:15">
       <c r="A293" t="s">
         <v>4116</v>
       </c>
@@ -35840,7 +36430,7 @@
         <v>4130</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:15">
       <c r="A294" t="s">
         <v>4131</v>
       </c>
@@ -35887,7 +36477,7 @@
         <v>4145</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:15">
       <c r="A295" t="s">
         <v>4146</v>
       </c>
@@ -35934,7 +36524,7 @@
         <v>4147</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:15">
       <c r="A296" t="s">
         <v>4160</v>
       </c>
@@ -35981,7 +36571,7 @@
         <v>4174</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:15">
       <c r="A297" t="s">
         <v>4175</v>
       </c>
@@ -36028,7 +36618,7 @@
         <v>4189</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:15">
       <c r="A298" t="s">
         <v>4190</v>
       </c>
@@ -36075,7 +36665,7 @@
         <v>4204</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:15">
       <c r="A299" t="s">
         <v>4205</v>
       </c>
@@ -36122,7 +36712,7 @@
         <v>4219</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:15">
       <c r="A300" t="s">
         <v>4220</v>
       </c>
@@ -36169,7 +36759,7 @@
         <v>4234</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:15">
       <c r="A301" t="s">
         <v>4235</v>
       </c>
@@ -36216,7 +36806,7 @@
         <v>4249</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:15">
       <c r="A302" t="s">
         <v>4250</v>
       </c>
@@ -36263,7 +36853,7 @@
         <v>4264</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:15">
       <c r="A303" t="s">
         <v>4265</v>
       </c>
@@ -36310,7 +36900,7 @@
         <v>4277</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:15">
       <c r="A304" t="s">
         <v>4278</v>
       </c>
@@ -36357,7 +36947,7 @@
         <v>4279</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:15">
       <c r="A305" t="s">
         <v>4290</v>
       </c>
@@ -36404,7 +36994,7 @@
         <v>4304</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:15">
       <c r="A306" t="s">
         <v>4305</v>
       </c>
@@ -36451,7 +37041,7 @@
         <v>4306</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:15">
       <c r="A307" t="s">
         <v>4319</v>
       </c>
@@ -36498,7 +37088,7 @@
         <v>4333</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:15">
       <c r="A308" t="s">
         <v>4334</v>
       </c>
@@ -36545,7 +37135,7 @@
         <v>4348</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:15">
       <c r="A309" t="s">
         <v>4349</v>
       </c>
@@ -36592,7 +37182,7 @@
         <v>4363</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:15">
       <c r="A310" t="s">
         <v>4364</v>
       </c>
@@ -36639,7 +37229,7 @@
         <v>4378</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:15">
       <c r="A311" t="s">
         <v>4379</v>
       </c>
@@ -36686,7 +37276,7 @@
         <v>4393</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:15">
       <c r="A312" t="s">
         <v>4394</v>
       </c>
@@ -36733,7 +37323,7 @@
         <v>4408</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:15">
       <c r="A313" t="s">
         <v>4409</v>
       </c>
@@ -36780,7 +37370,7 @@
         <v>4423</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:15">
       <c r="A314" t="s">
         <v>4424</v>
       </c>
@@ -36827,7 +37417,7 @@
         <v>4438</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:15">
       <c r="A315" t="s">
         <v>4439</v>
       </c>
@@ -36874,7 +37464,7 @@
         <v>4453</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:15">
       <c r="A316" t="s">
         <v>4454</v>
       </c>
@@ -36921,7 +37511,7 @@
         <v>4468</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:15">
       <c r="A317" t="s">
         <v>4469</v>
       </c>
@@ -36968,7 +37558,7 @@
         <v>4470</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:15">
       <c r="A318" t="s">
         <v>4483</v>
       </c>
@@ -37015,7 +37605,7 @@
         <v>4484</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:15">
       <c r="A319" t="s">
         <v>4497</v>
       </c>
@@ -37062,7 +37652,7 @@
         <v>4511</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:15">
       <c r="A320" t="s">
         <v>4512</v>
       </c>
@@ -37109,7 +37699,7 @@
         <v>4526</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:15">
       <c r="A321" t="s">
         <v>4527</v>
       </c>
@@ -37156,7 +37746,7 @@
         <v>4528</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:15">
       <c r="A322" t="s">
         <v>4541</v>
       </c>
@@ -37203,7 +37793,7 @@
         <v>4542</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:15">
       <c r="A323" t="s">
         <v>4555</v>
       </c>
@@ -37250,7 +37840,7 @@
         <v>4556</v>
       </c>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:15">
       <c r="A324" t="s">
         <v>4569</v>
       </c>
@@ -37297,7 +37887,7 @@
         <v>4570</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:15">
       <c r="A325" t="s">
         <v>4583</v>
       </c>
@@ -37344,7 +37934,7 @@
         <v>4597</v>
       </c>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:15">
       <c r="A326" t="s">
         <v>4598</v>
       </c>
@@ -37391,7 +37981,7 @@
         <v>4612</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:15">
       <c r="A327" t="s">
         <v>4613</v>
       </c>
@@ -37438,7 +38028,7 @@
         <v>4627</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:15">
       <c r="A328" t="s">
         <v>4628</v>
       </c>
@@ -37485,7 +38075,7 @@
         <v>4642</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:15">
       <c r="A329" t="s">
         <v>4643</v>
       </c>
@@ -37532,7 +38122,7 @@
         <v>4657</v>
       </c>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:15">
       <c r="A330" t="s">
         <v>4658</v>
       </c>
@@ -37579,7 +38169,7 @@
         <v>4672</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="331" spans="1:15">
       <c r="A331" t="s">
         <v>4673</v>
       </c>
@@ -37626,7 +38216,7 @@
         <v>4674</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:15">
       <c r="A332" t="s">
         <v>4687</v>
       </c>
@@ -37673,7 +38263,7 @@
         <v>4688</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:15">
       <c r="A333" t="s">
         <v>4701</v>
       </c>
@@ -37720,7 +38310,7 @@
         <v>4715</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:15">
       <c r="A334" t="s">
         <v>4716</v>
       </c>
@@ -37767,7 +38357,7 @@
         <v>4730</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="335" spans="1:15">
       <c r="A335" t="s">
         <v>4731</v>
       </c>
@@ -37814,7 +38404,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="336" spans="1:15">
       <c r="A336" t="s">
         <v>4745</v>
       </c>
@@ -37861,7 +38451,7 @@
         <v>4746</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="337" spans="1:15">
       <c r="A337" t="s">
         <v>4758</v>
       </c>
@@ -37908,7 +38498,7 @@
         <v>4772</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="338" spans="1:15">
       <c r="A338" t="s">
         <v>4773</v>
       </c>
@@ -37955,7 +38545,7 @@
         <v>4786</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="339" spans="1:15">
       <c r="A339" t="s">
         <v>4787</v>
       </c>
@@ -38002,7 +38592,7 @@
         <v>4790</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="340" spans="1:15">
       <c r="A340" t="s">
         <v>4799</v>
       </c>
@@ -38049,7 +38639,7 @@
         <v>4813</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="341" spans="1:15">
       <c r="A341" t="s">
         <v>4814</v>
       </c>
@@ -38096,7 +38686,7 @@
         <v>4828</v>
       </c>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="342" spans="1:15">
       <c r="A342" t="s">
         <v>4829</v>
       </c>
@@ -38143,7 +38733,7 @@
         <v>4830</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="343" spans="1:15">
       <c r="A343" t="s">
         <v>4839</v>
       </c>
@@ -38190,7 +38780,7 @@
         <v>4840</v>
       </c>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="344" spans="1:15">
       <c r="A344" t="s">
         <v>4853</v>
       </c>
@@ -38237,7 +38827,7 @@
         <v>4866</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="345" spans="1:15">
       <c r="A345" t="s">
         <v>4867</v>
       </c>
@@ -38284,7 +38874,7 @@
         <v>4868</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="346" spans="1:15">
       <c r="A346" t="s">
         <v>4881</v>
       </c>
@@ -38331,7 +38921,7 @@
         <v>4894</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="347" spans="1:15">
       <c r="A347" t="s">
         <v>4895</v>
       </c>
@@ -38378,7 +38968,7 @@
         <v>4896</v>
       </c>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="348" spans="1:15">
       <c r="A348" t="s">
         <v>4905</v>
       </c>
@@ -38425,7 +39015,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="349" spans="1:15">
       <c r="A349" t="s">
         <v>4920</v>
       </c>
@@ -38472,7 +39062,7 @@
         <v>4934</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="350" spans="1:15">
       <c r="A350" t="s">
         <v>4935</v>
       </c>
@@ -38519,7 +39109,7 @@
         <v>4949</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="351" spans="1:15">
       <c r="A351" t="s">
         <v>4950</v>
       </c>
@@ -38566,7 +39156,7 @@
         <v>4951</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="352" spans="1:15">
       <c r="A352" t="s">
         <v>4964</v>
       </c>
@@ -38613,7 +39203,7 @@
         <v>4977</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="353" spans="1:15">
       <c r="A353" t="s">
         <v>4978</v>
       </c>
@@ -38660,7 +39250,7 @@
         <v>4992</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="354" spans="1:15">
       <c r="A354" t="s">
         <v>4993</v>
       </c>
@@ -38707,7 +39297,7 @@
         <v>5007</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="355" spans="1:15">
       <c r="A355" t="s">
         <v>5008</v>
       </c>
@@ -38754,7 +39344,7 @@
         <v>5022</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="356" spans="1:15">
       <c r="A356" t="s">
         <v>5023</v>
       </c>
@@ -38801,7 +39391,7 @@
         <v>5037</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="357" spans="1:15">
       <c r="A357" t="s">
         <v>5038</v>
       </c>
@@ -38848,7 +39438,7 @@
         <v>5039</v>
       </c>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="358" spans="1:15">
       <c r="A358" t="s">
         <v>5052</v>
       </c>
@@ -38895,7 +39485,7 @@
         <v>5053</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="359" spans="1:15">
       <c r="A359" t="s">
         <v>5064</v>
       </c>
@@ -38942,7 +39532,7 @@
         <v>5076</v>
       </c>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="360" spans="1:15">
       <c r="A360" t="s">
         <v>5077</v>
       </c>
@@ -38989,7 +39579,7 @@
         <v>5091</v>
       </c>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="361" spans="1:15">
       <c r="A361" t="s">
         <v>5092</v>
       </c>
@@ -39036,7 +39626,7 @@
         <v>5093</v>
       </c>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="362" spans="1:15">
       <c r="A362" t="s">
         <v>5106</v>
       </c>
@@ -39083,7 +39673,7 @@
         <v>5120</v>
       </c>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="363" spans="1:15">
       <c r="A363" t="s">
         <v>5121</v>
       </c>
@@ -39130,7 +39720,7 @@
         <v>5135</v>
       </c>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="364" spans="1:15">
       <c r="A364" t="s">
         <v>5136</v>
       </c>
@@ -39177,7 +39767,7 @@
         <v>5137</v>
       </c>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="365" spans="1:15">
       <c r="A365" t="s">
         <v>5150</v>
       </c>
@@ -39224,7 +39814,7 @@
         <v>5164</v>
       </c>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="366" spans="1:15">
       <c r="A366" t="s">
         <v>5165</v>
       </c>
@@ -39271,7 +39861,7 @@
         <v>5166</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="367" spans="1:15">
       <c r="A367" t="s">
         <v>5179</v>
       </c>
@@ -39318,7 +39908,7 @@
         <v>5193</v>
       </c>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="368" spans="1:15">
       <c r="A368" t="s">
         <v>5194</v>
       </c>
@@ -39365,7 +39955,7 @@
         <v>5195</v>
       </c>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="369" spans="1:15">
       <c r="A369" t="s">
         <v>5208</v>
       </c>
@@ -39412,7 +40002,7 @@
         <v>5209</v>
       </c>
     </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="370" spans="1:15">
       <c r="A370" t="s">
         <v>5222</v>
       </c>
@@ -39459,7 +40049,7 @@
         <v>5223</v>
       </c>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="371" spans="1:15">
       <c r="A371" t="s">
         <v>5236</v>
       </c>
@@ -39506,7 +40096,7 @@
         <v>5237</v>
       </c>
     </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="372" spans="1:15">
       <c r="A372" t="s">
         <v>5248</v>
       </c>
@@ -39553,7 +40143,7 @@
         <v>5261</v>
       </c>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="373" spans="1:15">
       <c r="A373" t="s">
         <v>5262</v>
       </c>
@@ -39600,7 +40190,7 @@
         <v>5276</v>
       </c>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="374" spans="1:15">
       <c r="A374" t="s">
         <v>5277</v>
       </c>
@@ -39647,7 +40237,7 @@
         <v>5278</v>
       </c>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="375" spans="1:15">
       <c r="A375" t="s">
         <v>5291</v>
       </c>
@@ -39694,7 +40284,7 @@
         <v>5305</v>
       </c>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="376" spans="1:15">
       <c r="A376" t="s">
         <v>5306</v>
       </c>
@@ -39741,7 +40331,7 @@
         <v>5320</v>
       </c>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="377" spans="1:15">
       <c r="A377" t="s">
         <v>5321</v>
       </c>
@@ -39788,7 +40378,7 @@
         <v>5335</v>
       </c>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="378" spans="1:15">
       <c r="A378" t="s">
         <v>5336</v>
       </c>
@@ -39835,7 +40425,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="379" spans="1:15">
       <c r="A379" t="s">
         <v>5338</v>
       </c>
@@ -39882,7 +40472,7 @@
         <v>5352</v>
       </c>
     </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="380" spans="1:15">
       <c r="A380" t="s">
         <v>5353</v>
       </c>
@@ -39929,7 +40519,7 @@
         <v>5356</v>
       </c>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="381" spans="1:15">
       <c r="A381" t="s">
         <v>5365</v>
       </c>
@@ -39976,7 +40566,7 @@
         <v>5379</v>
       </c>
     </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="382" spans="1:15">
       <c r="A382" t="s">
         <v>5380</v>
       </c>
@@ -40023,7 +40613,7 @@
         <v>5390</v>
       </c>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="383" spans="1:15">
       <c r="A383" t="s">
         <v>5391</v>
       </c>
@@ -40070,7 +40660,7 @@
         <v>5405</v>
       </c>
     </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="384" spans="1:15">
       <c r="A384" t="s">
         <v>5406</v>
       </c>
@@ -40117,7 +40707,7 @@
         <v>5407</v>
       </c>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="385" spans="1:15">
       <c r="A385" t="s">
         <v>5418</v>
       </c>
@@ -40164,7 +40754,7 @@
         <v>5432</v>
       </c>
     </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="386" spans="1:15">
       <c r="A386" t="s">
         <v>5433</v>
       </c>
@@ -40211,7 +40801,7 @@
         <v>5447</v>
       </c>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="387" spans="1:15">
       <c r="A387" t="s">
         <v>5448</v>
       </c>
@@ -40258,7 +40848,7 @@
         <v>5449</v>
       </c>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="388" spans="1:15">
       <c r="A388" t="s">
         <v>5461</v>
       </c>
@@ -40305,7 +40895,7 @@
         <v>5474</v>
       </c>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="389" spans="1:15">
       <c r="A389" t="s">
         <v>5475</v>
       </c>
@@ -40352,7 +40942,7 @@
         <v>5489</v>
       </c>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="390" spans="1:15">
       <c r="A390" t="s">
         <v>5490</v>
       </c>
@@ -40399,7 +40989,7 @@
         <v>5504</v>
       </c>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="391" spans="1:15">
       <c r="A391" t="s">
         <v>5505</v>
       </c>
@@ -40446,7 +41036,7 @@
         <v>5506</v>
       </c>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="392" spans="1:15">
       <c r="A392" t="s">
         <v>5519</v>
       </c>
@@ -40493,7 +41083,7 @@
         <v>5520</v>
       </c>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="393" spans="1:15">
       <c r="A393" t="s">
         <v>5529</v>
       </c>
@@ -40540,7 +41130,7 @@
         <v>5543</v>
       </c>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="394" spans="1:15">
       <c r="A394" t="s">
         <v>5544</v>
       </c>
@@ -40587,7 +41177,7 @@
         <v>5558</v>
       </c>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="395" spans="1:15">
       <c r="A395" t="s">
         <v>5559</v>
       </c>
@@ -40634,7 +41224,7 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="396" spans="1:15">
       <c r="A396" t="s">
         <v>5573</v>
       </c>
@@ -40681,7 +41271,7 @@
         <v>5587</v>
       </c>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="397" spans="1:15">
       <c r="A397" t="s">
         <v>5588</v>
       </c>
@@ -40728,7 +41318,7 @@
         <v>5602</v>
       </c>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="398" spans="1:15">
       <c r="A398" t="s">
         <v>5603</v>
       </c>
@@ -40775,7 +41365,7 @@
         <v>5617</v>
       </c>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="399" spans="1:15">
       <c r="A399" t="s">
         <v>5618</v>
       </c>
@@ -40822,7 +41412,7 @@
         <v>5632</v>
       </c>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="400" spans="1:15">
       <c r="A400" t="s">
         <v>5633</v>
       </c>
@@ -40869,7 +41459,7 @@
         <v>5634</v>
       </c>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="401" spans="1:15">
       <c r="A401" t="s">
         <v>5647</v>
       </c>
@@ -40916,7 +41506,7 @@
         <v>5661</v>
       </c>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="402" spans="1:15">
       <c r="A402" t="s">
         <v>5662</v>
       </c>
@@ -40963,7 +41553,7 @@
         <v>5663</v>
       </c>
     </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="403" spans="1:15">
       <c r="A403" t="s">
         <v>5674</v>
       </c>
@@ -41010,7 +41600,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="404" spans="1:15">
       <c r="A404" t="s">
         <v>5687</v>
       </c>
@@ -41057,7 +41647,7 @@
         <v>5699</v>
       </c>
     </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="405" spans="1:15">
       <c r="A405" t="s">
         <v>5700</v>
       </c>
@@ -41104,7 +41694,7 @@
         <v>5714</v>
       </c>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="406" spans="1:15">
       <c r="A406" t="s">
         <v>5715</v>
       </c>
@@ -41151,7 +41741,7 @@
         <v>5729</v>
       </c>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="407" spans="1:15">
       <c r="A407" t="s">
         <v>5730</v>
       </c>
@@ -41198,7 +41788,7 @@
         <v>5744</v>
       </c>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="408" spans="1:15">
       <c r="A408" t="s">
         <v>5745</v>
       </c>
@@ -41245,7 +41835,7 @@
         <v>5746</v>
       </c>
     </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="409" spans="1:15">
       <c r="A409" t="s">
         <v>5759</v>
       </c>
@@ -41292,7 +41882,7 @@
         <v>5760</v>
       </c>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="410" spans="1:15">
       <c r="A410" t="s">
         <v>5772</v>
       </c>
@@ -41339,7 +41929,7 @@
         <v>5786</v>
       </c>
     </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="411" spans="1:15">
       <c r="A411" t="s">
         <v>5787</v>
       </c>
@@ -41386,7 +41976,7 @@
         <v>5801</v>
       </c>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="412" spans="1:15">
       <c r="A412" t="s">
         <v>5802</v>
       </c>
@@ -41433,7 +42023,7 @@
         <v>5816</v>
       </c>
     </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="413" spans="1:15">
       <c r="A413" t="s">
         <v>5817</v>
       </c>
@@ -41480,7 +42070,7 @@
         <v>5831</v>
       </c>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="414" spans="1:15">
       <c r="A414" t="s">
         <v>5832</v>
       </c>
@@ -41527,7 +42117,7 @@
         <v>5845</v>
       </c>
     </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="415" spans="1:15">
       <c r="A415" t="s">
         <v>5846</v>
       </c>
@@ -41574,7 +42164,7 @@
         <v>5860</v>
       </c>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="416" spans="1:15">
       <c r="A416" t="s">
         <v>5861</v>
       </c>
@@ -41621,7 +42211,7 @@
         <v>5874</v>
       </c>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="417" spans="1:15">
       <c r="A417" t="s">
         <v>5875</v>
       </c>
@@ -41668,7 +42258,7 @@
         <v>5889</v>
       </c>
     </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="418" spans="1:15">
       <c r="A418" t="s">
         <v>5890</v>
       </c>
@@ -41715,7 +42305,7 @@
         <v>5891</v>
       </c>
     </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="419" spans="1:15">
       <c r="A419" t="s">
         <v>5904</v>
       </c>
@@ -41762,7 +42352,7 @@
         <v>5905</v>
       </c>
     </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="420" spans="1:15">
       <c r="A420" t="s">
         <v>5918</v>
       </c>
@@ -41809,7 +42399,7 @@
         <v>5932</v>
       </c>
     </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="421" spans="1:15">
       <c r="A421" t="s">
         <v>5933</v>
       </c>
@@ -41856,7 +42446,7 @@
         <v>5947</v>
       </c>
     </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="422" spans="1:15">
       <c r="A422" t="s">
         <v>5948</v>
       </c>
@@ -41903,7 +42493,7 @@
         <v>5962</v>
       </c>
     </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="423" spans="1:15">
       <c r="A423" t="s">
         <v>5963</v>
       </c>
@@ -41950,7 +42540,7 @@
         <v>5977</v>
       </c>
     </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="424" spans="1:15">
       <c r="A424" t="s">
         <v>5978</v>
       </c>
@@ -41997,7 +42587,7 @@
         <v>5992</v>
       </c>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="425" spans="1:15">
       <c r="A425" t="s">
         <v>5993</v>
       </c>
@@ -42044,7 +42634,7 @@
         <v>6007</v>
       </c>
     </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="426" spans="1:15">
       <c r="A426" t="s">
         <v>6008</v>
       </c>
@@ -42091,7 +42681,7 @@
         <v>6009</v>
       </c>
     </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="427" spans="1:15">
       <c r="A427" t="s">
         <v>6022</v>
       </c>
@@ -42138,7 +42728,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="428" spans="1:15">
       <c r="A428" t="s">
         <v>6031</v>
       </c>
@@ -42185,7 +42775,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="429" spans="1:15">
       <c r="A429" t="s">
         <v>6038</v>
       </c>
@@ -42232,7 +42822,7 @@
         <v>6039</v>
       </c>
     </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="430" spans="1:15">
       <c r="A430" t="s">
         <v>6052</v>
       </c>
@@ -42279,7 +42869,7 @@
         <v>6066</v>
       </c>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="431" spans="1:15">
       <c r="A431" t="s">
         <v>6067</v>
       </c>
@@ -42326,7 +42916,7 @@
         <v>6068</v>
       </c>
     </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="432" spans="1:15">
       <c r="A432" t="s">
         <v>6080</v>
       </c>
@@ -42373,7 +42963,7 @@
         <v>6094</v>
       </c>
     </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="433" spans="1:15">
       <c r="A433" t="s">
         <v>6095</v>
       </c>
@@ -42420,7 +43010,7 @@
         <v>6109</v>
       </c>
     </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="434" spans="1:15">
       <c r="A434" t="s">
         <v>6110</v>
       </c>
@@ -42467,7 +43057,7 @@
         <v>6124</v>
       </c>
     </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="435" spans="1:15">
       <c r="A435" t="s">
         <v>6125</v>
       </c>
@@ -42514,7 +43104,7 @@
         <v>6139</v>
       </c>
     </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="436" spans="1:15">
       <c r="A436" t="s">
         <v>6140</v>
       </c>
@@ -42561,7 +43151,7 @@
         <v>4052</v>
       </c>
     </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="437" spans="1:15">
       <c r="A437" t="s">
         <v>6153</v>
       </c>
@@ -42608,7 +43198,7 @@
         <v>4107</v>
       </c>
     </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="438" spans="1:15">
       <c r="A438" t="s">
         <v>6159</v>
       </c>
@@ -42655,7 +43245,7 @@
         <v>3990</v>
       </c>
     </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="439" spans="1:15">
       <c r="A439" t="s">
         <v>6167</v>
       </c>
@@ -42702,7 +43292,7 @@
         <v>4145</v>
       </c>
     </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="440" spans="1:15">
       <c r="A440" t="s">
         <v>6179</v>
       </c>
@@ -42749,7 +43339,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="441" spans="1:15">
       <c r="A441" t="s">
         <v>6193</v>
       </c>
@@ -42796,7 +43386,7 @@
         <v>4147</v>
       </c>
     </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="442" spans="1:15">
       <c r="A442" t="s">
         <v>6206</v>
       </c>
@@ -42843,7 +43433,7 @@
         <v>4174</v>
       </c>
     </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="443" spans="1:15">
       <c r="A443" t="s">
         <v>6211</v>
       </c>
@@ -42890,7 +43480,7 @@
         <v>6225</v>
       </c>
     </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="444" spans="1:15">
       <c r="A444" t="s">
         <v>6226</v>
       </c>
@@ -42937,7 +43527,7 @@
         <v>6240</v>
       </c>
     </row>
-    <row r="445" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="445" spans="1:15">
       <c r="A445" t="s">
         <v>6241</v>
       </c>
@@ -42984,7 +43574,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="446" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="446" spans="1:15">
       <c r="A446" t="s">
         <v>6256</v>
       </c>
@@ -43031,7 +43621,7 @@
         <v>6270</v>
       </c>
     </row>
-    <row r="447" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="447" spans="1:15">
       <c r="A447" t="s">
         <v>6271</v>
       </c>
@@ -43078,7 +43668,7 @@
         <v>6284</v>
       </c>
     </row>
-    <row r="448" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="448" spans="1:15">
       <c r="A448" t="s">
         <v>6285</v>
       </c>
@@ -43125,7 +43715,7 @@
         <v>6298</v>
       </c>
     </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="449" spans="1:15">
       <c r="A449" t="s">
         <v>6299</v>
       </c>
@@ -43172,7 +43762,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="450" spans="1:15">
       <c r="A450" t="s">
         <v>6305</v>
       </c>
@@ -43219,7 +43809,7 @@
         <v>6312</v>
       </c>
     </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="451" spans="1:15">
       <c r="A451" t="s">
         <v>6313</v>
       </c>
@@ -43266,7 +43856,7 @@
         <v>6327</v>
       </c>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="452" spans="1:15">
       <c r="A452" t="s">
         <v>6328</v>
       </c>
@@ -43313,7 +43903,7 @@
         <v>6342</v>
       </c>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="453" spans="1:15">
       <c r="A453" t="s">
         <v>6343</v>
       </c>
@@ -43360,7 +43950,7 @@
         <v>6344</v>
       </c>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="454" spans="1:15">
       <c r="A454" t="s">
         <v>6357</v>
       </c>
@@ -43407,7 +43997,7 @@
         <v>6360</v>
       </c>
     </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="455" spans="1:15">
       <c r="A455" t="s">
         <v>6370</v>
       </c>
@@ -43454,7 +44044,7 @@
         <v>6371</v>
       </c>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="456" spans="1:15">
       <c r="A456" t="s">
         <v>6382</v>
       </c>
@@ -43501,7 +44091,7 @@
         <v>6385</v>
       </c>
     </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="457" spans="1:15">
       <c r="A457" t="s">
         <v>6396</v>
       </c>
@@ -43548,7 +44138,7 @@
         <v>6410</v>
       </c>
     </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="458" spans="1:15">
       <c r="A458" t="s">
         <v>6411</v>
       </c>
@@ -43595,7 +44185,7 @@
         <v>6425</v>
       </c>
     </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="459" spans="1:15">
       <c r="A459" t="s">
         <v>6426</v>
       </c>
@@ -43642,7 +44232,7 @@
         <v>6440</v>
       </c>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="460" spans="1:15">
       <c r="A460" t="s">
         <v>6441</v>
       </c>
@@ -43689,7 +44279,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="461" spans="1:15">
       <c r="A461" t="s">
         <v>6456</v>
       </c>
@@ -43736,7 +44326,7 @@
         <v>6470</v>
       </c>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="462" spans="1:15">
       <c r="A462" t="s">
         <v>6471</v>
       </c>
@@ -43783,7 +44373,7 @@
         <v>6485</v>
       </c>
     </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="463" spans="1:15">
       <c r="A463" t="s">
         <v>6486</v>
       </c>
@@ -43830,7 +44420,7 @@
         <v>6499</v>
       </c>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="464" spans="1:15">
       <c r="A464" t="s">
         <v>6500</v>
       </c>
@@ -43877,7 +44467,7 @@
         <v>6513</v>
       </c>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="465" spans="1:15">
       <c r="A465" t="s">
         <v>6514</v>
       </c>
@@ -43924,7 +44514,7 @@
         <v>6528</v>
       </c>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="466" spans="1:15">
       <c r="A466" t="s">
         <v>6529</v>
       </c>
@@ -43971,7 +44561,7 @@
         <v>6543</v>
       </c>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="467" spans="1:15">
       <c r="A467" t="s">
         <v>6544</v>
       </c>
@@ -44018,7 +44608,7 @@
         <v>6557</v>
       </c>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="468" spans="1:15">
       <c r="A468" t="s">
         <v>6558</v>
       </c>
@@ -44065,7 +44655,7 @@
         <v>6572</v>
       </c>
     </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="469" spans="1:15">
       <c r="A469" t="s">
         <v>6573</v>
       </c>
@@ -44112,7 +44702,7 @@
         <v>6574</v>
       </c>
     </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="470" spans="1:15">
       <c r="A470" t="s">
         <v>6586</v>
       </c>
@@ -44159,7 +44749,7 @@
         <v>6587</v>
       </c>
     </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="471" spans="1:15">
       <c r="A471" t="s">
         <v>6600</v>
       </c>
@@ -44206,7 +44796,7 @@
         <v>6601</v>
       </c>
     </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="472" spans="1:15">
       <c r="A472" t="s">
         <v>6613</v>
       </c>
@@ -44253,7 +44843,7 @@
         <v>6618</v>
       </c>
     </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="473" spans="1:15">
       <c r="A473" t="s">
         <v>6619</v>
       </c>
@@ -44300,7 +44890,7 @@
         <v>6633</v>
       </c>
     </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="474" spans="1:15">
       <c r="A474" t="s">
         <v>6634</v>
       </c>
@@ -44347,7 +44937,7 @@
         <v>6648</v>
       </c>
     </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="475" spans="1:15">
       <c r="A475" t="s">
         <v>6649</v>
       </c>
@@ -44394,7 +44984,7 @@
         <v>6658</v>
       </c>
     </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="476" spans="1:15">
       <c r="A476" t="s">
         <v>6659</v>
       </c>
@@ -44441,7 +45031,7 @@
         <v>6672</v>
       </c>
     </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="477" spans="1:15">
       <c r="A477" t="s">
         <v>6673</v>
       </c>
@@ -44488,7 +45078,7 @@
         <v>6687</v>
       </c>
     </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="478" spans="1:15">
       <c r="A478" t="s">
         <v>6688</v>
       </c>
@@ -44535,7 +45125,7 @@
         <v>6702</v>
       </c>
     </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="479" spans="1:15">
       <c r="A479" t="s">
         <v>6703</v>
       </c>
@@ -44582,7 +45172,7 @@
         <v>6717</v>
       </c>
     </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="480" spans="1:15">
       <c r="A480" t="s">
         <v>6718</v>
       </c>
@@ -44629,7 +45219,7 @@
         <v>6732</v>
       </c>
     </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="481" spans="1:15">
       <c r="A481" t="s">
         <v>6733</v>
       </c>
@@ -44676,7 +45266,7 @@
         <v>6747</v>
       </c>
     </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="482" spans="1:15">
       <c r="A482" t="s">
         <v>6748</v>
       </c>
@@ -44723,7 +45313,7 @@
         <v>6762</v>
       </c>
     </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="483" spans="1:15">
       <c r="A483" t="s">
         <v>6763</v>
       </c>
@@ -44770,7 +45360,7 @@
         <v>6777</v>
       </c>
     </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="484" spans="1:15">
       <c r="A484" t="s">
         <v>6778</v>
       </c>
@@ -44817,7 +45407,7 @@
         <v>6792</v>
       </c>
     </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="485" spans="1:15">
       <c r="A485" t="s">
         <v>6793</v>
       </c>
@@ -44864,7 +45454,7 @@
         <v>6807</v>
       </c>
     </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="486" spans="1:15">
       <c r="A486" t="s">
         <v>6808</v>
       </c>
@@ -44911,7 +45501,7 @@
         <v>6822</v>
       </c>
     </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="487" spans="1:15">
       <c r="A487" t="s">
         <v>6823</v>
       </c>
@@ -44958,7 +45548,7 @@
         <v>6837</v>
       </c>
     </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="488" spans="1:15">
       <c r="A488" t="s">
         <v>6838</v>
       </c>
@@ -45005,7 +45595,7 @@
         <v>6852</v>
       </c>
     </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="489" spans="1:15">
       <c r="A489" t="s">
         <v>6853</v>
       </c>
@@ -45052,7 +45642,7 @@
         <v>6867</v>
       </c>
     </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="490" spans="1:15">
       <c r="A490" t="s">
         <v>6868</v>
       </c>
@@ -45099,7 +45689,7 @@
         <v>6882</v>
       </c>
     </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="491" spans="1:15">
       <c r="A491" t="s">
         <v>6883</v>
       </c>
@@ -45146,7 +45736,7 @@
         <v>6897</v>
       </c>
     </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="492" spans="1:15">
       <c r="A492" t="s">
         <v>6898</v>
       </c>
@@ -45193,7 +45783,7 @@
         <v>6912</v>
       </c>
     </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="493" spans="1:15">
       <c r="A493" t="s">
         <v>6913</v>
       </c>
@@ -45240,7 +45830,7 @@
         <v>6927</v>
       </c>
     </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="494" spans="1:15">
       <c r="A494" t="s">
         <v>6928</v>
       </c>
@@ -45287,7 +45877,7 @@
         <v>6942</v>
       </c>
     </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="495" spans="1:15">
       <c r="A495" t="s">
         <v>6943</v>
       </c>
@@ -45334,7 +45924,7 @@
         <v>6957</v>
       </c>
     </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="496" spans="1:15">
       <c r="A496" t="s">
         <v>6958</v>
       </c>
@@ -45381,7 +45971,7 @@
         <v>6972</v>
       </c>
     </row>
-    <row r="497" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="497" spans="1:15">
       <c r="A497" t="s">
         <v>6973</v>
       </c>
@@ -45428,7 +46018,7 @@
         <v>6987</v>
       </c>
     </row>
-    <row r="498" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="498" spans="1:15">
       <c r="A498" t="s">
         <v>6988</v>
       </c>
@@ -45475,7 +46065,7 @@
         <v>7002</v>
       </c>
     </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="499" spans="1:15">
       <c r="A499" t="s">
         <v>7003</v>
       </c>
@@ -45522,7 +46112,7 @@
         <v>7004</v>
       </c>
     </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="500" spans="1:15">
       <c r="A500" t="s">
         <v>7017</v>
       </c>
@@ -45569,7 +46159,7 @@
         <v>7019</v>
       </c>
     </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="501" spans="1:15">
       <c r="A501" t="s">
         <v>7020</v>
       </c>
@@ -45616,7 +46206,7 @@
         <v>7034</v>
       </c>
     </row>
-    <row r="502" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="502" spans="1:15">
       <c r="A502" t="s">
         <v>7035</v>
       </c>
@@ -45663,7 +46253,7 @@
         <v>7049</v>
       </c>
     </row>
-    <row r="503" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="503" spans="1:15">
       <c r="A503" t="s">
         <v>7050</v>
       </c>
@@ -45710,7 +46300,7 @@
         <v>7052</v>
       </c>
     </row>
-    <row r="504" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="504" spans="1:15">
       <c r="A504" t="s">
         <v>7053</v>
       </c>
@@ -45757,7 +46347,7 @@
         <v>7054</v>
       </c>
     </row>
-    <row r="505" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="505" spans="1:15">
       <c r="A505" t="s">
         <v>7067</v>
       </c>
@@ -45804,7 +46394,7 @@
         <v>7081</v>
       </c>
     </row>
-    <row r="506" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="506" spans="1:15">
       <c r="A506" t="s">
         <v>7082</v>
       </c>
@@ -45851,7 +46441,7 @@
         <v>7096</v>
       </c>
     </row>
-    <row r="507" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="507" spans="1:15">
       <c r="A507" t="s">
         <v>7097</v>
       </c>
@@ -45898,7 +46488,7 @@
         <v>7111</v>
       </c>
     </row>
-    <row r="508" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="508" spans="1:15">
       <c r="A508" t="s">
         <v>7112</v>
       </c>
@@ -45945,7 +46535,7 @@
         <v>7126</v>
       </c>
     </row>
-    <row r="509" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="509" spans="1:15">
       <c r="A509" t="s">
         <v>7127</v>
       </c>
@@ -45992,7 +46582,7 @@
         <v>7141</v>
       </c>
     </row>
-    <row r="510" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="510" spans="1:15">
       <c r="A510" t="s">
         <v>7142</v>
       </c>
@@ -46039,7 +46629,7 @@
         <v>7143</v>
       </c>
     </row>
-    <row r="511" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="511" spans="1:15">
       <c r="A511" t="s">
         <v>7156</v>
       </c>
@@ -46086,7 +46676,7 @@
         <v>7157</v>
       </c>
     </row>
-    <row r="512" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="512" spans="1:15">
       <c r="A512" t="s">
         <v>7159</v>
       </c>
@@ -46133,7 +46723,7 @@
         <v>7160</v>
       </c>
     </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="513" spans="1:15">
       <c r="A513" t="s">
         <v>7161</v>
       </c>
@@ -46180,7 +46770,7 @@
         <v>7162</v>
       </c>
     </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="514" spans="1:15">
       <c r="A514" t="s">
         <v>7163</v>
       </c>
@@ -46191,280 +46781,280 @@
         <v>7164</v>
       </c>
       <c r="D514" t="s">
-        <v>7164</v>
+        <v>7165</v>
       </c>
       <c r="E514" t="s">
-        <v>7164</v>
+        <v>7165</v>
       </c>
       <c r="F514" t="s">
-        <v>7164</v>
+        <v>7165</v>
       </c>
       <c r="G514" t="s">
-        <v>7164</v>
+        <v>7165</v>
       </c>
       <c r="H514" t="s">
-        <v>7164</v>
+        <v>7165</v>
       </c>
       <c r="I514" t="s">
-        <v>7164</v>
+        <v>7165</v>
       </c>
       <c r="J514" t="s">
-        <v>7164</v>
+        <v>7165</v>
       </c>
       <c r="K514" t="s">
-        <v>7164</v>
+        <v>7165</v>
       </c>
       <c r="L514" t="s">
-        <v>7164</v>
+        <v>7165</v>
       </c>
       <c r="M514" t="s">
-        <v>7164</v>
+        <v>7165</v>
       </c>
       <c r="N514" t="s">
-        <v>7164</v>
+        <v>7165</v>
       </c>
       <c r="O514" t="s">
-        <v>7164</v>
-      </c>
-    </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.15">
+        <v>7165</v>
+      </c>
+    </row>
+    <row r="515" spans="1:15">
       <c r="A515" s="1" t="s">
-        <v>7165</v>
+        <v>7166</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>7166</v>
+        <v>7167</v>
       </c>
       <c r="C515" s="1" t="s">
-        <v>7166</v>
+        <v>7167</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>7166</v>
+        <v>7167</v>
       </c>
       <c r="E515" s="1" t="s">
-        <v>7166</v>
+        <v>7167</v>
       </c>
       <c r="F515" s="1" t="s">
-        <v>7166</v>
+        <v>7167</v>
       </c>
       <c r="G515" s="1" t="s">
-        <v>7166</v>
+        <v>7167</v>
       </c>
       <c r="H515" s="1" t="s">
-        <v>7166</v>
+        <v>7167</v>
       </c>
       <c r="I515" s="1" t="s">
-        <v>7166</v>
+        <v>7167</v>
       </c>
       <c r="J515" s="1" t="s">
-        <v>7166</v>
+        <v>7167</v>
       </c>
       <c r="K515" s="1" t="s">
-        <v>7166</v>
+        <v>7167</v>
       </c>
       <c r="L515" s="1" t="s">
-        <v>7166</v>
+        <v>7167</v>
       </c>
       <c r="M515" s="1" t="s">
-        <v>7166</v>
+        <v>7167</v>
       </c>
       <c r="N515" s="1" t="s">
-        <v>7166</v>
+        <v>7167</v>
       </c>
       <c r="O515" s="1" t="s">
-        <v>7166</v>
-      </c>
-    </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.15">
+        <v>7167</v>
+      </c>
+    </row>
+    <row r="516" spans="1:15">
       <c r="A516" s="1" t="s">
+        <v>7168</v>
+      </c>
+      <c r="B516" s="2" t="s">
+        <v>7169</v>
+      </c>
+      <c r="C516" s="2" t="s">
+        <v>7169</v>
+      </c>
+      <c r="D516" s="2" t="s">
+        <v>7169</v>
+      </c>
+      <c r="E516" s="2" t="s">
+        <v>7169</v>
+      </c>
+      <c r="F516" s="2" t="s">
+        <v>7169</v>
+      </c>
+      <c r="G516" s="2" t="s">
+        <v>7169</v>
+      </c>
+      <c r="H516" s="2" t="s">
+        <v>7169</v>
+      </c>
+      <c r="I516" s="2" t="s">
+        <v>7169</v>
+      </c>
+      <c r="J516" s="2" t="s">
+        <v>7169</v>
+      </c>
+      <c r="K516" s="2" t="s">
+        <v>7169</v>
+      </c>
+      <c r="L516" s="2" t="s">
+        <v>7169</v>
+      </c>
+      <c r="M516" s="2" t="s">
+        <v>7169</v>
+      </c>
+      <c r="N516" s="2" t="s">
+        <v>7169</v>
+      </c>
+      <c r="O516" s="2" t="s">
+        <v>7169</v>
+      </c>
+    </row>
+    <row r="517" spans="1:15">
+      <c r="A517" s="3" t="s">
+        <v>7170</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="C517" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="D517" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="E517" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="F517" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="G517" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="H517" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="I517" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="J517" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="K517" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="L517" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="M517" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="N517" s="1" t="s">
+        <v>7171</v>
+      </c>
+      <c r="O517" s="1" t="s">
+        <v>7171</v>
+      </c>
+    </row>
+    <row r="518" spans="1:15">
+      <c r="A518" s="1" t="s">
+        <v>7172</v>
+      </c>
+      <c r="B518" s="1" t="s">
         <v>7173</v>
       </c>
-      <c r="B516" s="1" t="s">
-        <v>7180</v>
-      </c>
-      <c r="C516" s="1" t="s">
-        <v>7180</v>
-      </c>
-      <c r="D516" s="1" t="s">
-        <v>7180</v>
-      </c>
-      <c r="E516" s="1" t="s">
-        <v>7180</v>
-      </c>
-      <c r="F516" s="1" t="s">
-        <v>7180</v>
-      </c>
-      <c r="G516" s="1" t="s">
-        <v>7180</v>
-      </c>
-      <c r="H516" s="1" t="s">
-        <v>7180</v>
-      </c>
-      <c r="I516" s="1" t="s">
-        <v>7180</v>
-      </c>
-      <c r="J516" s="1" t="s">
-        <v>7180</v>
-      </c>
-      <c r="K516" s="1" t="s">
-        <v>7180</v>
-      </c>
-      <c r="L516" s="1" t="s">
-        <v>7180</v>
-      </c>
-      <c r="M516" s="1" t="s">
-        <v>7180</v>
-      </c>
-      <c r="N516" s="1" t="s">
-        <v>7180</v>
-      </c>
-      <c r="O516" s="1" t="s">
-        <v>7180</v>
-      </c>
-    </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A517" s="2" t="s">
-        <v>7167</v>
-      </c>
-      <c r="B517" s="1" t="s">
-        <v>7170</v>
-      </c>
-      <c r="C517" s="1" t="s">
-        <v>7170</v>
-      </c>
-      <c r="D517" s="1" t="s">
-        <v>7170</v>
-      </c>
-      <c r="E517" s="1" t="s">
-        <v>7170</v>
-      </c>
-      <c r="F517" s="1" t="s">
-        <v>7170</v>
-      </c>
-      <c r="G517" s="1" t="s">
-        <v>7170</v>
-      </c>
-      <c r="H517" s="1" t="s">
-        <v>7170</v>
-      </c>
-      <c r="I517" s="1" t="s">
-        <v>7170</v>
-      </c>
-      <c r="J517" s="1" t="s">
-        <v>7170</v>
-      </c>
-      <c r="K517" s="1" t="s">
-        <v>7170</v>
-      </c>
-      <c r="L517" s="1" t="s">
-        <v>7170</v>
-      </c>
-      <c r="M517" s="1" t="s">
-        <v>7170</v>
-      </c>
-      <c r="N517" s="1" t="s">
-        <v>7170</v>
-      </c>
-      <c r="O517" s="1" t="s">
-        <v>7170</v>
-      </c>
-    </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A518" s="1" t="s">
-        <v>7168</v>
-      </c>
-      <c r="B518" s="1" t="s">
-        <v>7171</v>
-      </c>
       <c r="C518" s="1" t="s">
-        <v>7171</v>
+        <v>7173</v>
       </c>
       <c r="D518" s="1" t="s">
-        <v>7171</v>
+        <v>7173</v>
       </c>
       <c r="E518" s="1" t="s">
-        <v>7171</v>
+        <v>7173</v>
       </c>
       <c r="F518" s="1" t="s">
-        <v>7171</v>
+        <v>7173</v>
       </c>
       <c r="G518" s="1" t="s">
-        <v>7171</v>
+        <v>7173</v>
       </c>
       <c r="H518" s="1" t="s">
-        <v>7171</v>
+        <v>7173</v>
       </c>
       <c r="I518" s="1" t="s">
-        <v>7171</v>
+        <v>7173</v>
       </c>
       <c r="J518" s="1" t="s">
-        <v>7171</v>
+        <v>7173</v>
       </c>
       <c r="K518" s="1" t="s">
-        <v>7171</v>
+        <v>7173</v>
       </c>
       <c r="L518" s="1" t="s">
-        <v>7171</v>
+        <v>7173</v>
       </c>
       <c r="M518" s="1" t="s">
-        <v>7171</v>
+        <v>7173</v>
       </c>
       <c r="N518" s="1" t="s">
-        <v>7171</v>
+        <v>7173</v>
       </c>
       <c r="O518" s="1" t="s">
-        <v>7171</v>
-      </c>
-    </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.15">
+        <v>7173</v>
+      </c>
+    </row>
+    <row r="519" spans="1:15">
       <c r="A519" s="1" t="s">
-        <v>7169</v>
+        <v>7174</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>7172</v>
+        <v>7175</v>
       </c>
       <c r="C519" s="1" t="s">
-        <v>7172</v>
+        <v>7175</v>
       </c>
       <c r="D519" s="1" t="s">
-        <v>7172</v>
+        <v>7175</v>
       </c>
       <c r="E519" s="1" t="s">
-        <v>7172</v>
+        <v>7175</v>
       </c>
       <c r="F519" s="1" t="s">
-        <v>7172</v>
+        <v>7175</v>
       </c>
       <c r="G519" s="1" t="s">
-        <v>7172</v>
+        <v>7175</v>
       </c>
       <c r="H519" s="1" t="s">
-        <v>7172</v>
+        <v>7175</v>
       </c>
       <c r="I519" s="1" t="s">
-        <v>7172</v>
+        <v>7175</v>
       </c>
       <c r="J519" s="1" t="s">
-        <v>7172</v>
+        <v>7175</v>
       </c>
       <c r="K519" s="1" t="s">
-        <v>7172</v>
+        <v>7175</v>
       </c>
       <c r="L519" s="1" t="s">
-        <v>7172</v>
+        <v>7175</v>
       </c>
       <c r="M519" s="1" t="s">
-        <v>7172</v>
+        <v>7175</v>
       </c>
       <c r="N519" s="1" t="s">
-        <v>7172</v>
+        <v>7175</v>
       </c>
       <c r="O519" s="1" t="s">
-        <v>7172</v>
-      </c>
-    </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.15">
+        <v>7175</v>
+      </c>
+    </row>
+    <row r="520" spans="1:15">
       <c r="A520" s="1" t="s">
-        <v>7174</v>
+        <v>7176</v>
       </c>
       <c r="B520" s="1" t="s">
         <v>7177</v>
@@ -46509,336 +47099,336 @@
         <v>7177</v>
       </c>
     </row>
-    <row r="521" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="521" spans="1:15">
       <c r="A521" s="1" t="s">
-        <v>7175</v>
+        <v>7178</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>7178</v>
+        <v>7179</v>
       </c>
       <c r="C521" s="1" t="s">
-        <v>7178</v>
+        <v>7179</v>
       </c>
       <c r="D521" s="1" t="s">
-        <v>7178</v>
+        <v>7179</v>
       </c>
       <c r="E521" s="1" t="s">
-        <v>7178</v>
+        <v>7179</v>
       </c>
       <c r="F521" s="1" t="s">
-        <v>7178</v>
+        <v>7179</v>
       </c>
       <c r="G521" s="1" t="s">
-        <v>7178</v>
+        <v>7179</v>
       </c>
       <c r="H521" s="1" t="s">
-        <v>7178</v>
+        <v>7179</v>
       </c>
       <c r="I521" s="1" t="s">
-        <v>7178</v>
+        <v>7179</v>
       </c>
       <c r="J521" s="1" t="s">
-        <v>7178</v>
+        <v>7179</v>
       </c>
       <c r="K521" s="1" t="s">
-        <v>7178</v>
+        <v>7179</v>
       </c>
       <c r="L521" s="1" t="s">
-        <v>7178</v>
+        <v>7179</v>
       </c>
       <c r="M521" s="1" t="s">
-        <v>7178</v>
+        <v>7179</v>
       </c>
       <c r="N521" s="1" t="s">
-        <v>7178</v>
+        <v>7179</v>
       </c>
       <c r="O521" s="1" t="s">
-        <v>7178</v>
-      </c>
-    </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.15">
+        <v>7179</v>
+      </c>
+    </row>
+    <row r="522" spans="1:15">
       <c r="A522" s="1" t="s">
-        <v>7176</v>
+        <v>7180</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>7179</v>
+        <v>7181</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>7179</v>
+        <v>7181</v>
       </c>
       <c r="D522" s="1" t="s">
-        <v>7179</v>
+        <v>7181</v>
       </c>
       <c r="E522" s="1" t="s">
-        <v>7179</v>
+        <v>7181</v>
       </c>
       <c r="F522" s="1" t="s">
-        <v>7179</v>
+        <v>7181</v>
       </c>
       <c r="G522" s="1" t="s">
-        <v>7179</v>
+        <v>7181</v>
       </c>
       <c r="H522" s="1" t="s">
-        <v>7179</v>
+        <v>7181</v>
       </c>
       <c r="I522" s="1" t="s">
-        <v>7179</v>
+        <v>7181</v>
       </c>
       <c r="J522" s="1" t="s">
-        <v>7179</v>
+        <v>7181</v>
       </c>
       <c r="K522" s="1" t="s">
-        <v>7179</v>
+        <v>7181</v>
       </c>
       <c r="L522" s="1" t="s">
-        <v>7179</v>
+        <v>7181</v>
       </c>
       <c r="M522" s="1" t="s">
-        <v>7179</v>
+        <v>7181</v>
       </c>
       <c r="N522" s="1" t="s">
-        <v>7179</v>
+        <v>7181</v>
       </c>
       <c r="O522" s="1" t="s">
-        <v>7179</v>
-      </c>
-    </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.15">
+        <v>7181</v>
+      </c>
+    </row>
+    <row r="523" spans="1:15">
       <c r="A523" s="1" t="s">
+        <v>7182</v>
+      </c>
+      <c r="B523" s="1" t="s">
         <v>7183</v>
       </c>
-      <c r="B523" s="1" t="s">
+      <c r="C523" s="1" t="s">
+        <v>7183</v>
+      </c>
+      <c r="D523" s="1" t="s">
+        <v>7183</v>
+      </c>
+      <c r="E523" s="1" t="s">
+        <v>7183</v>
+      </c>
+      <c r="F523" s="1" t="s">
+        <v>7183</v>
+      </c>
+      <c r="G523" s="1" t="s">
+        <v>7183</v>
+      </c>
+      <c r="H523" s="1" t="s">
+        <v>7183</v>
+      </c>
+      <c r="I523" s="1" t="s">
+        <v>7183</v>
+      </c>
+      <c r="J523" s="1" t="s">
+        <v>7183</v>
+      </c>
+      <c r="K523" s="1" t="s">
+        <v>7183</v>
+      </c>
+      <c r="L523" s="1" t="s">
+        <v>7183</v>
+      </c>
+      <c r="M523" s="1" t="s">
+        <v>7183</v>
+      </c>
+      <c r="N523" s="1" t="s">
+        <v>7183</v>
+      </c>
+      <c r="O523" s="1" t="s">
+        <v>7183</v>
+      </c>
+    </row>
+    <row r="524" spans="1:15">
+      <c r="A524" s="4" t="s">
         <v>7184</v>
       </c>
-      <c r="C523" s="1" t="s">
-        <v>7184</v>
-      </c>
-      <c r="D523" s="1" t="s">
-        <v>7184</v>
-      </c>
-      <c r="E523" s="1" t="s">
-        <v>7184</v>
-      </c>
-      <c r="F523" s="1" t="s">
-        <v>7184</v>
-      </c>
-      <c r="G523" s="1" t="s">
-        <v>7184</v>
-      </c>
-      <c r="H523" s="1" t="s">
-        <v>7184</v>
-      </c>
-      <c r="I523" s="1" t="s">
-        <v>7184</v>
-      </c>
-      <c r="J523" s="1" t="s">
-        <v>7184</v>
-      </c>
-      <c r="K523" s="1" t="s">
-        <v>7184</v>
-      </c>
-      <c r="L523" s="1" t="s">
-        <v>7184</v>
-      </c>
-      <c r="M523" s="1" t="s">
-        <v>7184</v>
-      </c>
-      <c r="N523" s="1" t="s">
-        <v>7184</v>
-      </c>
-      <c r="O523" s="1" t="s">
-        <v>7184</v>
-      </c>
-    </row>
-    <row r="524" spans="1:15" ht="15" x14ac:dyDescent="0.15">
-      <c r="A524" s="3" t="s">
+      <c r="B524" s="1" t="s">
+        <v>7185</v>
+      </c>
+      <c r="C524" s="1" t="s">
+        <v>7185</v>
+      </c>
+      <c r="D524" s="1" t="s">
+        <v>7185</v>
+      </c>
+      <c r="E524" s="1" t="s">
+        <v>7185</v>
+      </c>
+      <c r="F524" s="1" t="s">
+        <v>7185</v>
+      </c>
+      <c r="G524" s="1" t="s">
+        <v>7185</v>
+      </c>
+      <c r="H524" s="1" t="s">
+        <v>7185</v>
+      </c>
+      <c r="I524" s="1" t="s">
+        <v>7185</v>
+      </c>
+      <c r="J524" s="1" t="s">
+        <v>7185</v>
+      </c>
+      <c r="K524" s="1" t="s">
+        <v>7185</v>
+      </c>
+      <c r="L524" s="1" t="s">
+        <v>7185</v>
+      </c>
+      <c r="M524" s="1" t="s">
+        <v>7185</v>
+      </c>
+      <c r="N524" s="1" t="s">
+        <v>7185</v>
+      </c>
+      <c r="O524" s="1" t="s">
+        <v>7185</v>
+      </c>
+    </row>
+    <row r="525" spans="1:15">
+      <c r="A525" s="1" t="s">
+        <v>7186</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>7187</v>
+      </c>
+      <c r="C525" s="1" t="s">
+        <v>7187</v>
+      </c>
+      <c r="D525" s="1" t="s">
+        <v>7187</v>
+      </c>
+      <c r="E525" s="1" t="s">
+        <v>7187</v>
+      </c>
+      <c r="F525" s="1" t="s">
+        <v>7187</v>
+      </c>
+      <c r="G525" s="1" t="s">
+        <v>7187</v>
+      </c>
+      <c r="H525" s="1" t="s">
+        <v>7187</v>
+      </c>
+      <c r="I525" s="1" t="s">
+        <v>7187</v>
+      </c>
+      <c r="J525" s="1" t="s">
+        <v>7187</v>
+      </c>
+      <c r="K525" s="1" t="s">
+        <v>7187</v>
+      </c>
+      <c r="L525" s="1" t="s">
+        <v>7187</v>
+      </c>
+      <c r="M525" s="1" t="s">
+        <v>7187</v>
+      </c>
+      <c r="N525" s="1" t="s">
+        <v>7187</v>
+      </c>
+      <c r="O525" s="1" t="s">
+        <v>7187</v>
+      </c>
+    </row>
+    <row r="526" spans="1:15">
+      <c r="A526" s="1" t="s">
+        <v>7188</v>
+      </c>
+      <c r="B526" s="1" t="s">
         <v>7189</v>
       </c>
-      <c r="B524" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="C524" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="D524" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="E524" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="F524" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="G524" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="H524" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="I524" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="J524" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="K524" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="L524" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="M524" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="N524" s="1" t="s">
-        <v>7181</v>
-      </c>
-      <c r="O524" s="1" t="s">
-        <v>7181</v>
-      </c>
-    </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A525" s="1" t="s">
+      <c r="C526" s="1" t="s">
+        <v>7189</v>
+      </c>
+      <c r="D526" s="1" t="s">
+        <v>7189</v>
+      </c>
+      <c r="E526" s="1" t="s">
+        <v>7189</v>
+      </c>
+      <c r="F526" s="1" t="s">
+        <v>7189</v>
+      </c>
+      <c r="G526" s="1" t="s">
+        <v>7189</v>
+      </c>
+      <c r="H526" s="1" t="s">
+        <v>7189</v>
+      </c>
+      <c r="I526" s="1" t="s">
+        <v>7189</v>
+      </c>
+      <c r="J526" s="1" t="s">
+        <v>7189</v>
+      </c>
+      <c r="K526" s="1" t="s">
+        <v>7189</v>
+      </c>
+      <c r="L526" s="1" t="s">
+        <v>7189</v>
+      </c>
+      <c r="M526" s="1" t="s">
+        <v>7189</v>
+      </c>
+      <c r="N526" s="1" t="s">
+        <v>7189</v>
+      </c>
+      <c r="O526" s="1" t="s">
+        <v>7189</v>
+      </c>
+    </row>
+    <row r="527" spans="1:15">
+      <c r="A527" s="1" t="s">
         <v>7190</v>
       </c>
-      <c r="B525" s="1" t="s">
-        <v>7182</v>
-      </c>
-      <c r="C525" s="1" t="s">
-        <v>7182</v>
-      </c>
-      <c r="D525" s="1" t="s">
-        <v>7182</v>
-      </c>
-      <c r="E525" s="1" t="s">
-        <v>7182</v>
-      </c>
-      <c r="F525" s="1" t="s">
-        <v>7182</v>
-      </c>
-      <c r="G525" s="1" t="s">
-        <v>7182</v>
-      </c>
-      <c r="H525" s="1" t="s">
-        <v>7182</v>
-      </c>
-      <c r="I525" s="1" t="s">
-        <v>7182</v>
-      </c>
-      <c r="J525" s="1" t="s">
-        <v>7182</v>
-      </c>
-      <c r="K525" s="1" t="s">
-        <v>7182</v>
-      </c>
-      <c r="L525" s="1" t="s">
-        <v>7182</v>
-      </c>
-      <c r="M525" s="1" t="s">
-        <v>7182</v>
-      </c>
-      <c r="N525" s="1" t="s">
-        <v>7182</v>
-      </c>
-      <c r="O525" s="1" t="s">
-        <v>7182</v>
-      </c>
-    </row>
-    <row r="526" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A526" s="1" t="s">
-        <v>7185</v>
-      </c>
-      <c r="B526" s="1" t="s">
-        <v>7186</v>
-      </c>
-      <c r="C526" s="1" t="s">
-        <v>7186</v>
-      </c>
-      <c r="D526" s="1" t="s">
-        <v>7186</v>
-      </c>
-      <c r="E526" s="1" t="s">
-        <v>7186</v>
-      </c>
-      <c r="F526" s="1" t="s">
-        <v>7186</v>
-      </c>
-      <c r="G526" s="1" t="s">
-        <v>7186</v>
-      </c>
-      <c r="H526" s="1" t="s">
-        <v>7186</v>
-      </c>
-      <c r="I526" s="1" t="s">
-        <v>7186</v>
-      </c>
-      <c r="J526" s="1" t="s">
-        <v>7186</v>
-      </c>
-      <c r="K526" s="1" t="s">
-        <v>7186</v>
-      </c>
-      <c r="L526" s="1" t="s">
-        <v>7186</v>
-      </c>
-      <c r="M526" s="1" t="s">
-        <v>7186</v>
-      </c>
-      <c r="N526" s="1" t="s">
-        <v>7186</v>
-      </c>
-      <c r="O526" s="1" t="s">
-        <v>7186</v>
-      </c>
-    </row>
-    <row r="527" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A527" s="1" t="s">
-        <v>7187</v>
-      </c>
       <c r="B527" s="1" t="s">
-        <v>7188</v>
+        <v>7191</v>
       </c>
       <c r="C527" s="1" t="s">
-        <v>7188</v>
+        <v>7191</v>
       </c>
       <c r="D527" s="1" t="s">
-        <v>7188</v>
+        <v>7191</v>
       </c>
       <c r="E527" s="1" t="s">
-        <v>7188</v>
+        <v>7191</v>
       </c>
       <c r="F527" s="1" t="s">
-        <v>7188</v>
+        <v>7191</v>
       </c>
       <c r="G527" s="1" t="s">
-        <v>7188</v>
+        <v>7191</v>
       </c>
       <c r="H527" s="1" t="s">
-        <v>7188</v>
+        <v>7191</v>
       </c>
       <c r="I527" s="1" t="s">
-        <v>7188</v>
+        <v>7191</v>
       </c>
       <c r="J527" s="1" t="s">
-        <v>7188</v>
+        <v>7191</v>
       </c>
       <c r="K527" s="1" t="s">
-        <v>7188</v>
+        <v>7191</v>
       </c>
       <c r="L527" s="1" t="s">
-        <v>7188</v>
+        <v>7191</v>
       </c>
       <c r="M527" s="1" t="s">
-        <v>7188</v>
+        <v>7191</v>
       </c>
       <c r="N527" s="1" t="s">
-        <v>7188</v>
+        <v>7191</v>
       </c>
       <c r="O527" s="1" t="s">
-        <v>7188</v>
-      </c>
-    </row>
-    <row r="528" spans="1:15" x14ac:dyDescent="0.15">
+        <v>7191</v>
+      </c>
+    </row>
+    <row r="528" spans="1:15">
       <c r="A528" s="1" t="s">
         <v>7192</v>
       </c>
@@ -46846,51 +47436,51 @@
         <v>7193</v>
       </c>
       <c r="C528" s="1" t="s">
-        <v>7191</v>
+        <v>7194</v>
       </c>
       <c r="D528" s="1" t="s">
-        <v>7191</v>
+        <v>7194</v>
       </c>
       <c r="E528" s="1" t="s">
-        <v>7191</v>
+        <v>7194</v>
       </c>
       <c r="F528" s="1" t="s">
-        <v>7191</v>
+        <v>7194</v>
       </c>
       <c r="G528" s="1" t="s">
-        <v>7191</v>
+        <v>7194</v>
       </c>
       <c r="H528" s="1" t="s">
-        <v>7191</v>
+        <v>7194</v>
       </c>
       <c r="I528" s="1" t="s">
-        <v>7191</v>
+        <v>7194</v>
       </c>
       <c r="J528" s="1" t="s">
-        <v>7191</v>
+        <v>7194</v>
       </c>
       <c r="K528" s="1" t="s">
-        <v>7191</v>
+        <v>7194</v>
       </c>
       <c r="L528" s="1" t="s">
-        <v>7191</v>
+        <v>7194</v>
       </c>
       <c r="M528" s="1" t="s">
-        <v>7191</v>
+        <v>7194</v>
       </c>
       <c r="N528" s="1" t="s">
-        <v>7191</v>
+        <v>7194</v>
       </c>
       <c r="O528" s="1" t="s">
-        <v>7191</v>
+        <v>7194</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A279:O449 A450 C450:O450 A451:O499 C118:O118 A504:O510 A503 A501:O502 A500 A252:O276 A277 C277 A1:O117 A118 A119:O250 A251" numberStoredAsText="1"/>
+    <ignoredError sqref="A251 A119:O250 A118 A1:O117 C277 A277 A252:O276 A500 A501:O502 A503 A504:O510 C118:O118 A451:O499 C450:O450 A450 A279:O449" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>